--- a/2026/ЗАВОДЫ/Останкино/филиалы НВ/10,26/20,10,26 Останкино СЫРЫ/дв 20,10,26 бррсч ост сыр.xlsx
+++ b/2026/ЗАВОДЫ/Останкино/филиалы НВ/10,26/20,10,26 Останкино СЫРЫ/дв 20,10,26 бррсч ост сыр.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\WORK\2025_05\в бланки заводов\Останкино СЫР\OrderCheeseInForm\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\WORK\2025_05\2026\ЗАВОДЫ\Останкино\филиалы НВ\10,26\20,10,26 Останкино СЫРЫ\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ED052728-0F13-4A91-A4A5-E85CD4407B3B}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2A142DA9-CBEC-45DB-8994-11605782BE45}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -22,7 +22,7 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet!$A$3:$AK$55</definedName>
   </definedNames>
-  <calcPr calcId="181029"/>
+  <calcPr calcId="181029" refMode="R1C1"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -402,8 +402,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="1">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="0_ ;[Red]\-0\ "/>
+    <numFmt numFmtId="165" formatCode="0.0"/>
   </numFmts>
   <fonts count="9" x14ac:knownFonts="1">
     <font>
@@ -543,7 +544,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1"/>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="27">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
     <xf numFmtId="164" fontId="1" fillId="0" borderId="1" xfId="1" applyNumberFormat="1"/>
     <xf numFmtId="164" fontId="2" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
@@ -569,6 +570,8 @@
     <xf numFmtId="164" fontId="8" fillId="4" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="1" fillId="0" borderId="1" xfId="1" applyNumberFormat="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Arial10px" xfId="1" xr:uid="{00000000-0005-0000-0000-000001000000}"/>
@@ -3038,7 +3041,8 @@
     <col min="26" max="35" width="6" customWidth="1"/>
     <col min="36" max="36" width="29.28515625" customWidth="1"/>
     <col min="37" max="38" width="7" customWidth="1"/>
-    <col min="39" max="53" width="8" customWidth="1"/>
+    <col min="39" max="39" width="8" style="26" customWidth="1"/>
+    <col min="40" max="53" width="8" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:53" x14ac:dyDescent="0.25">
@@ -3080,7 +3084,7 @@
       <c r="AJ1" s="1"/>
       <c r="AK1" s="1"/>
       <c r="AL1" s="1"/>
-      <c r="AM1" s="1"/>
+      <c r="AM1" s="25"/>
       <c r="AN1" s="1"/>
       <c r="AO1" s="1"/>
       <c r="AP1" s="1"/>
@@ -3143,7 +3147,7 @@
       <c r="AL2" s="1" t="s">
         <v>107</v>
       </c>
-      <c r="AM2" s="1"/>
+      <c r="AM2" s="25"/>
       <c r="AN2" s="1"/>
       <c r="AO2" s="1"/>
       <c r="AP2" s="1"/>
@@ -3274,7 +3278,7 @@
       <c r="AL3" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="AM3" s="1"/>
+      <c r="AM3" s="25"/>
       <c r="AN3" s="1"/>
       <c r="AO3" s="1"/>
       <c r="AP3" s="1"/>
@@ -3365,7 +3369,7 @@
       <c r="AL4" s="1" t="s">
         <v>106</v>
       </c>
-      <c r="AM4" s="1"/>
+      <c r="AM4" s="25"/>
       <c r="AN4" s="1"/>
       <c r="AO4" s="1"/>
       <c r="AP4" s="1"/>
@@ -3501,7 +3505,7 @@
         <f>SUM(AL6:AL500)</f>
         <v>342</v>
       </c>
-      <c r="AM5" s="1"/>
+      <c r="AM5" s="25"/>
       <c r="AN5" s="1"/>
       <c r="AO5" s="1"/>
       <c r="AP5" s="1"/>
@@ -3617,7 +3621,7 @@
         <f>G6*U6</f>
         <v>0</v>
       </c>
-      <c r="AM6" s="1"/>
+      <c r="AM6" s="25"/>
       <c r="AN6" s="1"/>
       <c r="AO6" s="1"/>
       <c r="AP6" s="1"/>
@@ -3731,7 +3735,7 @@
         <f t="shared" ref="AL7:AL55" si="7">G7*U7</f>
         <v>0</v>
       </c>
-      <c r="AM7" s="1"/>
+      <c r="AM7" s="25"/>
       <c r="AN7" s="1"/>
       <c r="AO7" s="1"/>
       <c r="AP7" s="1"/>
@@ -3847,7 +3851,7 @@
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="AM8" s="1"/>
+      <c r="AM8" s="25"/>
       <c r="AN8" s="1"/>
       <c r="AO8" s="1"/>
       <c r="AP8" s="1"/>
@@ -3977,7 +3981,10 @@
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="AM9" s="1"/>
+      <c r="AM9" s="25">
+        <f>P9/Z9</f>
+        <v>2.6735425022009194</v>
+      </c>
       <c r="AN9" s="1"/>
       <c r="AO9" s="1"/>
       <c r="AP9" s="1"/>
@@ -4094,7 +4101,7 @@
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="AM10" s="1"/>
+      <c r="AM10" s="25"/>
       <c r="AN10" s="1"/>
       <c r="AO10" s="1"/>
       <c r="AP10" s="1"/>
@@ -4212,7 +4219,7 @@
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="AM11" s="1"/>
+      <c r="AM11" s="25"/>
       <c r="AN11" s="1"/>
       <c r="AO11" s="1"/>
       <c r="AP11" s="1"/>
@@ -4339,7 +4346,7 @@
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="AM12" s="1"/>
+      <c r="AM12" s="25"/>
       <c r="AN12" s="1"/>
       <c r="AO12" s="1"/>
       <c r="AP12" s="1"/>
@@ -4466,7 +4473,7 @@
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="AM13" s="1"/>
+      <c r="AM13" s="25"/>
       <c r="AN13" s="1"/>
       <c r="AO13" s="1"/>
       <c r="AP13" s="1"/>
@@ -4593,7 +4600,7 @@
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="AM14" s="1"/>
+      <c r="AM14" s="25"/>
       <c r="AN14" s="1"/>
       <c r="AO14" s="1"/>
       <c r="AP14" s="1"/>
@@ -4718,7 +4725,7 @@
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="AM15" s="1"/>
+      <c r="AM15" s="25"/>
       <c r="AN15" s="1"/>
       <c r="AO15" s="1"/>
       <c r="AP15" s="1"/>
@@ -4832,7 +4839,7 @@
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="AM16" s="1"/>
+      <c r="AM16" s="25"/>
       <c r="AN16" s="1"/>
       <c r="AO16" s="1"/>
       <c r="AP16" s="1"/>
@@ -4959,7 +4966,7 @@
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="AM17" s="1"/>
+      <c r="AM17" s="25"/>
       <c r="AN17" s="1"/>
       <c r="AO17" s="1"/>
       <c r="AP17" s="1"/>
@@ -5077,7 +5084,7 @@
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="AM18" s="1"/>
+      <c r="AM18" s="25"/>
       <c r="AN18" s="1"/>
       <c r="AO18" s="1"/>
       <c r="AP18" s="1"/>
@@ -5195,7 +5202,7 @@
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="AM19" s="1"/>
+      <c r="AM19" s="25"/>
       <c r="AN19" s="1"/>
       <c r="AO19" s="1"/>
       <c r="AP19" s="1"/>
@@ -5324,7 +5331,7 @@
         <f t="shared" si="7"/>
         <v>162</v>
       </c>
-      <c r="AM20" s="1"/>
+      <c r="AM20" s="25"/>
       <c r="AN20" s="1"/>
       <c r="AO20" s="1"/>
       <c r="AP20" s="1"/>
@@ -5456,7 +5463,7 @@
         <f t="shared" si="7"/>
         <v>180</v>
       </c>
-      <c r="AM21" s="1"/>
+      <c r="AM21" s="25"/>
       <c r="AN21" s="1"/>
       <c r="AO21" s="1"/>
       <c r="AP21" s="1"/>
@@ -5579,7 +5586,7 @@
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="AM22" s="1"/>
+      <c r="AM22" s="25"/>
       <c r="AN22" s="1"/>
       <c r="AO22" s="1"/>
       <c r="AP22" s="1"/>
@@ -5695,7 +5702,7 @@
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="AM23" s="1"/>
+      <c r="AM23" s="25"/>
       <c r="AN23" s="1"/>
       <c r="AO23" s="1"/>
       <c r="AP23" s="1"/>
@@ -5813,7 +5820,7 @@
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="AM24" s="1"/>
+      <c r="AM24" s="25"/>
       <c r="AN24" s="1"/>
       <c r="AO24" s="1"/>
       <c r="AP24" s="1"/>
@@ -5932,7 +5939,7 @@
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="AM25" s="1"/>
+      <c r="AM25" s="25"/>
       <c r="AN25" s="1"/>
       <c r="AO25" s="1"/>
       <c r="AP25" s="1"/>
@@ -6040,7 +6047,7 @@
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="AM26" s="1"/>
+      <c r="AM26" s="25"/>
       <c r="AN26" s="1"/>
       <c r="AO26" s="1"/>
       <c r="AP26" s="1"/>
@@ -6158,7 +6165,7 @@
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="AM27" s="1"/>
+      <c r="AM27" s="25"/>
       <c r="AN27" s="1"/>
       <c r="AO27" s="1"/>
       <c r="AP27" s="1"/>
@@ -6287,7 +6294,7 @@
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="AM28" s="1"/>
+      <c r="AM28" s="25"/>
       <c r="AN28" s="1"/>
       <c r="AO28" s="1"/>
       <c r="AP28" s="1"/>
@@ -6403,7 +6410,7 @@
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="AM29" s="1"/>
+      <c r="AM29" s="25"/>
       <c r="AN29" s="1"/>
       <c r="AO29" s="1"/>
       <c r="AP29" s="1"/>
@@ -6528,7 +6535,7 @@
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="AM30" s="1"/>
+      <c r="AM30" s="25"/>
       <c r="AN30" s="1"/>
       <c r="AO30" s="1"/>
       <c r="AP30" s="1"/>
@@ -6650,7 +6657,7 @@
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="AM31" s="1"/>
+      <c r="AM31" s="25"/>
       <c r="AN31" s="1"/>
       <c r="AO31" s="1"/>
       <c r="AP31" s="1"/>
@@ -6776,7 +6783,7 @@
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="AM32" s="1"/>
+      <c r="AM32" s="25"/>
       <c r="AN32" s="1"/>
       <c r="AO32" s="1"/>
       <c r="AP32" s="1"/>
@@ -6900,7 +6907,7 @@
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="AM33" s="1"/>
+      <c r="AM33" s="25"/>
       <c r="AN33" s="1"/>
       <c r="AO33" s="1"/>
       <c r="AP33" s="1"/>
@@ -7026,7 +7033,7 @@
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="AM34" s="1"/>
+      <c r="AM34" s="25"/>
       <c r="AN34" s="1"/>
       <c r="AO34" s="1"/>
       <c r="AP34" s="1"/>
@@ -7155,7 +7162,7 @@
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="AM35" s="1"/>
+      <c r="AM35" s="25"/>
       <c r="AN35" s="1"/>
       <c r="AO35" s="1"/>
       <c r="AP35" s="1"/>
@@ -7282,7 +7289,7 @@
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="AM36" s="1"/>
+      <c r="AM36" s="25"/>
       <c r="AN36" s="1"/>
       <c r="AO36" s="1"/>
       <c r="AP36" s="1"/>
@@ -7409,7 +7416,7 @@
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="AM37" s="1"/>
+      <c r="AM37" s="25"/>
       <c r="AN37" s="1"/>
       <c r="AO37" s="1"/>
       <c r="AP37" s="1"/>
@@ -7527,7 +7534,7 @@
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="AM38" s="1"/>
+      <c r="AM38" s="25"/>
       <c r="AN38" s="1"/>
       <c r="AO38" s="1"/>
       <c r="AP38" s="1"/>
@@ -7643,7 +7650,7 @@
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="AM39" s="1"/>
+      <c r="AM39" s="25"/>
       <c r="AN39" s="1"/>
       <c r="AO39" s="1"/>
       <c r="AP39" s="1"/>
@@ -7768,7 +7775,7 @@
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="AM40" s="1"/>
+      <c r="AM40" s="25"/>
       <c r="AN40" s="1"/>
       <c r="AO40" s="1"/>
       <c r="AP40" s="1"/>
@@ -7886,7 +7893,7 @@
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="AM41" s="1"/>
+      <c r="AM41" s="25"/>
       <c r="AN41" s="1"/>
       <c r="AO41" s="1"/>
       <c r="AP41" s="1"/>
@@ -8002,7 +8009,7 @@
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="AM42" s="1"/>
+      <c r="AM42" s="25"/>
       <c r="AN42" s="1"/>
       <c r="AO42" s="1"/>
       <c r="AP42" s="1"/>
@@ -8116,7 +8123,7 @@
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="AM43" s="1"/>
+      <c r="AM43" s="25"/>
       <c r="AN43" s="1"/>
       <c r="AO43" s="1"/>
       <c r="AP43" s="1"/>
@@ -8243,7 +8250,7 @@
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="AM44" s="1"/>
+      <c r="AM44" s="25"/>
       <c r="AN44" s="1"/>
       <c r="AO44" s="1"/>
       <c r="AP44" s="1"/>
@@ -8361,7 +8368,7 @@
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="AM45" s="1"/>
+      <c r="AM45" s="25"/>
       <c r="AN45" s="1"/>
       <c r="AO45" s="1"/>
       <c r="AP45" s="1"/>
@@ -8481,7 +8488,7 @@
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="AM46" s="1"/>
+      <c r="AM46" s="25"/>
       <c r="AN46" s="1"/>
       <c r="AO46" s="1"/>
       <c r="AP46" s="1"/>
@@ -8595,7 +8602,7 @@
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="AM47" s="1"/>
+      <c r="AM47" s="25"/>
       <c r="AN47" s="1"/>
       <c r="AO47" s="1"/>
       <c r="AP47" s="1"/>
@@ -8720,7 +8727,7 @@
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="AM48" s="1"/>
+      <c r="AM48" s="25"/>
       <c r="AN48" s="1"/>
       <c r="AO48" s="1"/>
       <c r="AP48" s="1"/>
@@ -8841,7 +8848,7 @@
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="AM49" s="1"/>
+      <c r="AM49" s="25"/>
       <c r="AN49" s="1"/>
       <c r="AO49" s="1"/>
       <c r="AP49" s="1"/>
@@ -8949,7 +8956,7 @@
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="AM50" s="1"/>
+      <c r="AM50" s="25"/>
       <c r="AN50" s="1"/>
       <c r="AO50" s="1"/>
       <c r="AP50" s="1"/>
@@ -9075,7 +9082,7 @@
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="AM51" s="1"/>
+      <c r="AM51" s="25"/>
       <c r="AN51" s="1"/>
       <c r="AO51" s="1"/>
       <c r="AP51" s="1"/>
@@ -9200,7 +9207,7 @@
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="AM52" s="1"/>
+      <c r="AM52" s="25"/>
       <c r="AN52" s="1"/>
       <c r="AO52" s="1"/>
       <c r="AP52" s="1"/>
@@ -9310,7 +9317,7 @@
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="AM53" s="1"/>
+      <c r="AM53" s="25"/>
       <c r="AN53" s="1"/>
       <c r="AO53" s="1"/>
       <c r="AP53" s="1"/>
@@ -9420,7 +9427,7 @@
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="AM54" s="1"/>
+      <c r="AM54" s="25"/>
       <c r="AN54" s="1"/>
       <c r="AO54" s="1"/>
       <c r="AP54" s="1"/>
@@ -9547,7 +9554,7 @@
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="AM55" s="1"/>
+      <c r="AM55" s="25"/>
       <c r="AN55" s="1"/>
       <c r="AO55" s="1"/>
       <c r="AP55" s="1"/>
@@ -9602,7 +9609,7 @@
       <c r="AJ56" s="1"/>
       <c r="AK56" s="1"/>
       <c r="AL56" s="1"/>
-      <c r="AM56" s="1"/>
+      <c r="AM56" s="25"/>
       <c r="AN56" s="1"/>
       <c r="AO56" s="1"/>
       <c r="AP56" s="1"/>
@@ -9657,7 +9664,7 @@
       <c r="AJ57" s="1"/>
       <c r="AK57" s="1"/>
       <c r="AL57" s="1"/>
-      <c r="AM57" s="1"/>
+      <c r="AM57" s="25"/>
       <c r="AN57" s="1"/>
       <c r="AO57" s="1"/>
       <c r="AP57" s="1"/>
@@ -9712,7 +9719,7 @@
       <c r="AJ58" s="1"/>
       <c r="AK58" s="1"/>
       <c r="AL58" s="1"/>
-      <c r="AM58" s="1"/>
+      <c r="AM58" s="25"/>
       <c r="AN58" s="1"/>
       <c r="AO58" s="1"/>
       <c r="AP58" s="1"/>
@@ -9767,7 +9774,7 @@
       <c r="AJ59" s="1"/>
       <c r="AK59" s="1"/>
       <c r="AL59" s="1"/>
-      <c r="AM59" s="1"/>
+      <c r="AM59" s="25"/>
       <c r="AN59" s="1"/>
       <c r="AO59" s="1"/>
       <c r="AP59" s="1"/>
@@ -9822,7 +9829,7 @@
       <c r="AJ60" s="1"/>
       <c r="AK60" s="1"/>
       <c r="AL60" s="1"/>
-      <c r="AM60" s="1"/>
+      <c r="AM60" s="25"/>
       <c r="AN60" s="1"/>
       <c r="AO60" s="1"/>
       <c r="AP60" s="1"/>
@@ -9877,7 +9884,7 @@
       <c r="AJ61" s="1"/>
       <c r="AK61" s="1"/>
       <c r="AL61" s="1"/>
-      <c r="AM61" s="1"/>
+      <c r="AM61" s="25"/>
       <c r="AN61" s="1"/>
       <c r="AO61" s="1"/>
       <c r="AP61" s="1"/>
@@ -9932,7 +9939,7 @@
       <c r="AJ62" s="1"/>
       <c r="AK62" s="1"/>
       <c r="AL62" s="1"/>
-      <c r="AM62" s="1"/>
+      <c r="AM62" s="25"/>
       <c r="AN62" s="1"/>
       <c r="AO62" s="1"/>
       <c r="AP62" s="1"/>
@@ -9987,7 +9994,7 @@
       <c r="AJ63" s="1"/>
       <c r="AK63" s="1"/>
       <c r="AL63" s="1"/>
-      <c r="AM63" s="1"/>
+      <c r="AM63" s="25"/>
       <c r="AN63" s="1"/>
       <c r="AO63" s="1"/>
       <c r="AP63" s="1"/>
@@ -10042,7 +10049,7 @@
       <c r="AJ64" s="1"/>
       <c r="AK64" s="1"/>
       <c r="AL64" s="1"/>
-      <c r="AM64" s="1"/>
+      <c r="AM64" s="25"/>
       <c r="AN64" s="1"/>
       <c r="AO64" s="1"/>
       <c r="AP64" s="1"/>
@@ -10097,7 +10104,7 @@
       <c r="AJ65" s="1"/>
       <c r="AK65" s="1"/>
       <c r="AL65" s="1"/>
-      <c r="AM65" s="1"/>
+      <c r="AM65" s="25"/>
       <c r="AN65" s="1"/>
       <c r="AO65" s="1"/>
       <c r="AP65" s="1"/>
@@ -10152,7 +10159,7 @@
       <c r="AJ66" s="1"/>
       <c r="AK66" s="1"/>
       <c r="AL66" s="1"/>
-      <c r="AM66" s="1"/>
+      <c r="AM66" s="25"/>
       <c r="AN66" s="1"/>
       <c r="AO66" s="1"/>
       <c r="AP66" s="1"/>
@@ -10207,7 +10214,7 @@
       <c r="AJ67" s="1"/>
       <c r="AK67" s="1"/>
       <c r="AL67" s="1"/>
-      <c r="AM67" s="1"/>
+      <c r="AM67" s="25"/>
       <c r="AN67" s="1"/>
       <c r="AO67" s="1"/>
       <c r="AP67" s="1"/>
@@ -10262,7 +10269,7 @@
       <c r="AJ68" s="1"/>
       <c r="AK68" s="1"/>
       <c r="AL68" s="1"/>
-      <c r="AM68" s="1"/>
+      <c r="AM68" s="25"/>
       <c r="AN68" s="1"/>
       <c r="AO68" s="1"/>
       <c r="AP68" s="1"/>
@@ -10317,7 +10324,7 @@
       <c r="AJ69" s="1"/>
       <c r="AK69" s="1"/>
       <c r="AL69" s="1"/>
-      <c r="AM69" s="1"/>
+      <c r="AM69" s="25"/>
       <c r="AN69" s="1"/>
       <c r="AO69" s="1"/>
       <c r="AP69" s="1"/>
@@ -10372,7 +10379,7 @@
       <c r="AJ70" s="1"/>
       <c r="AK70" s="1"/>
       <c r="AL70" s="1"/>
-      <c r="AM70" s="1"/>
+      <c r="AM70" s="25"/>
       <c r="AN70" s="1"/>
       <c r="AO70" s="1"/>
       <c r="AP70" s="1"/>
@@ -10427,7 +10434,7 @@
       <c r="AJ71" s="1"/>
       <c r="AK71" s="1"/>
       <c r="AL71" s="1"/>
-      <c r="AM71" s="1"/>
+      <c r="AM71" s="25"/>
       <c r="AN71" s="1"/>
       <c r="AO71" s="1"/>
       <c r="AP71" s="1"/>
@@ -10482,7 +10489,7 @@
       <c r="AJ72" s="1"/>
       <c r="AK72" s="1"/>
       <c r="AL72" s="1"/>
-      <c r="AM72" s="1"/>
+      <c r="AM72" s="25"/>
       <c r="AN72" s="1"/>
       <c r="AO72" s="1"/>
       <c r="AP72" s="1"/>
@@ -10537,7 +10544,7 @@
       <c r="AJ73" s="1"/>
       <c r="AK73" s="1"/>
       <c r="AL73" s="1"/>
-      <c r="AM73" s="1"/>
+      <c r="AM73" s="25"/>
       <c r="AN73" s="1"/>
       <c r="AO73" s="1"/>
       <c r="AP73" s="1"/>
@@ -10592,7 +10599,7 @@
       <c r="AJ74" s="1"/>
       <c r="AK74" s="1"/>
       <c r="AL74" s="1"/>
-      <c r="AM74" s="1"/>
+      <c r="AM74" s="25"/>
       <c r="AN74" s="1"/>
       <c r="AO74" s="1"/>
       <c r="AP74" s="1"/>
@@ -10647,7 +10654,7 @@
       <c r="AJ75" s="1"/>
       <c r="AK75" s="1"/>
       <c r="AL75" s="1"/>
-      <c r="AM75" s="1"/>
+      <c r="AM75" s="25"/>
       <c r="AN75" s="1"/>
       <c r="AO75" s="1"/>
       <c r="AP75" s="1"/>
@@ -10702,7 +10709,7 @@
       <c r="AJ76" s="1"/>
       <c r="AK76" s="1"/>
       <c r="AL76" s="1"/>
-      <c r="AM76" s="1"/>
+      <c r="AM76" s="25"/>
       <c r="AN76" s="1"/>
       <c r="AO76" s="1"/>
       <c r="AP76" s="1"/>
@@ -10757,7 +10764,7 @@
       <c r="AJ77" s="1"/>
       <c r="AK77" s="1"/>
       <c r="AL77" s="1"/>
-      <c r="AM77" s="1"/>
+      <c r="AM77" s="25"/>
       <c r="AN77" s="1"/>
       <c r="AO77" s="1"/>
       <c r="AP77" s="1"/>
@@ -10812,7 +10819,7 @@
       <c r="AJ78" s="1"/>
       <c r="AK78" s="1"/>
       <c r="AL78" s="1"/>
-      <c r="AM78" s="1"/>
+      <c r="AM78" s="25"/>
       <c r="AN78" s="1"/>
       <c r="AO78" s="1"/>
       <c r="AP78" s="1"/>
@@ -10867,7 +10874,7 @@
       <c r="AJ79" s="1"/>
       <c r="AK79" s="1"/>
       <c r="AL79" s="1"/>
-      <c r="AM79" s="1"/>
+      <c r="AM79" s="25"/>
       <c r="AN79" s="1"/>
       <c r="AO79" s="1"/>
       <c r="AP79" s="1"/>
@@ -10922,7 +10929,7 @@
       <c r="AJ80" s="1"/>
       <c r="AK80" s="1"/>
       <c r="AL80" s="1"/>
-      <c r="AM80" s="1"/>
+      <c r="AM80" s="25"/>
       <c r="AN80" s="1"/>
       <c r="AO80" s="1"/>
       <c r="AP80" s="1"/>
@@ -10977,7 +10984,7 @@
       <c r="AJ81" s="1"/>
       <c r="AK81" s="1"/>
       <c r="AL81" s="1"/>
-      <c r="AM81" s="1"/>
+      <c r="AM81" s="25"/>
       <c r="AN81" s="1"/>
       <c r="AO81" s="1"/>
       <c r="AP81" s="1"/>
@@ -11032,7 +11039,7 @@
       <c r="AJ82" s="1"/>
       <c r="AK82" s="1"/>
       <c r="AL82" s="1"/>
-      <c r="AM82" s="1"/>
+      <c r="AM82" s="25"/>
       <c r="AN82" s="1"/>
       <c r="AO82" s="1"/>
       <c r="AP82" s="1"/>
@@ -11087,7 +11094,7 @@
       <c r="AJ83" s="1"/>
       <c r="AK83" s="1"/>
       <c r="AL83" s="1"/>
-      <c r="AM83" s="1"/>
+      <c r="AM83" s="25"/>
       <c r="AN83" s="1"/>
       <c r="AO83" s="1"/>
       <c r="AP83" s="1"/>
@@ -11142,7 +11149,7 @@
       <c r="AJ84" s="1"/>
       <c r="AK84" s="1"/>
       <c r="AL84" s="1"/>
-      <c r="AM84" s="1"/>
+      <c r="AM84" s="25"/>
       <c r="AN84" s="1"/>
       <c r="AO84" s="1"/>
       <c r="AP84" s="1"/>
@@ -11197,7 +11204,7 @@
       <c r="AJ85" s="1"/>
       <c r="AK85" s="1"/>
       <c r="AL85" s="1"/>
-      <c r="AM85" s="1"/>
+      <c r="AM85" s="25"/>
       <c r="AN85" s="1"/>
       <c r="AO85" s="1"/>
       <c r="AP85" s="1"/>
@@ -11252,7 +11259,7 @@
       <c r="AJ86" s="1"/>
       <c r="AK86" s="1"/>
       <c r="AL86" s="1"/>
-      <c r="AM86" s="1"/>
+      <c r="AM86" s="25"/>
       <c r="AN86" s="1"/>
       <c r="AO86" s="1"/>
       <c r="AP86" s="1"/>
@@ -11307,7 +11314,7 @@
       <c r="AJ87" s="1"/>
       <c r="AK87" s="1"/>
       <c r="AL87" s="1"/>
-      <c r="AM87" s="1"/>
+      <c r="AM87" s="25"/>
       <c r="AN87" s="1"/>
       <c r="AO87" s="1"/>
       <c r="AP87" s="1"/>
@@ -11362,7 +11369,7 @@
       <c r="AJ88" s="1"/>
       <c r="AK88" s="1"/>
       <c r="AL88" s="1"/>
-      <c r="AM88" s="1"/>
+      <c r="AM88" s="25"/>
       <c r="AN88" s="1"/>
       <c r="AO88" s="1"/>
       <c r="AP88" s="1"/>
@@ -11417,7 +11424,7 @@
       <c r="AJ89" s="1"/>
       <c r="AK89" s="1"/>
       <c r="AL89" s="1"/>
-      <c r="AM89" s="1"/>
+      <c r="AM89" s="25"/>
       <c r="AN89" s="1"/>
       <c r="AO89" s="1"/>
       <c r="AP89" s="1"/>
@@ -11472,7 +11479,7 @@
       <c r="AJ90" s="1"/>
       <c r="AK90" s="1"/>
       <c r="AL90" s="1"/>
-      <c r="AM90" s="1"/>
+      <c r="AM90" s="25"/>
       <c r="AN90" s="1"/>
       <c r="AO90" s="1"/>
       <c r="AP90" s="1"/>
@@ -11527,7 +11534,7 @@
       <c r="AJ91" s="1"/>
       <c r="AK91" s="1"/>
       <c r="AL91" s="1"/>
-      <c r="AM91" s="1"/>
+      <c r="AM91" s="25"/>
       <c r="AN91" s="1"/>
       <c r="AO91" s="1"/>
       <c r="AP91" s="1"/>
@@ -11582,7 +11589,7 @@
       <c r="AJ92" s="1"/>
       <c r="AK92" s="1"/>
       <c r="AL92" s="1"/>
-      <c r="AM92" s="1"/>
+      <c r="AM92" s="25"/>
       <c r="AN92" s="1"/>
       <c r="AO92" s="1"/>
       <c r="AP92" s="1"/>
@@ -11637,7 +11644,7 @@
       <c r="AJ93" s="1"/>
       <c r="AK93" s="1"/>
       <c r="AL93" s="1"/>
-      <c r="AM93" s="1"/>
+      <c r="AM93" s="25"/>
       <c r="AN93" s="1"/>
       <c r="AO93" s="1"/>
       <c r="AP93" s="1"/>
@@ -11692,7 +11699,7 @@
       <c r="AJ94" s="1"/>
       <c r="AK94" s="1"/>
       <c r="AL94" s="1"/>
-      <c r="AM94" s="1"/>
+      <c r="AM94" s="25"/>
       <c r="AN94" s="1"/>
       <c r="AO94" s="1"/>
       <c r="AP94" s="1"/>
@@ -11747,7 +11754,7 @@
       <c r="AJ95" s="1"/>
       <c r="AK95" s="1"/>
       <c r="AL95" s="1"/>
-      <c r="AM95" s="1"/>
+      <c r="AM95" s="25"/>
       <c r="AN95" s="1"/>
       <c r="AO95" s="1"/>
       <c r="AP95" s="1"/>
@@ -11802,7 +11809,7 @@
       <c r="AJ96" s="1"/>
       <c r="AK96" s="1"/>
       <c r="AL96" s="1"/>
-      <c r="AM96" s="1"/>
+      <c r="AM96" s="25"/>
       <c r="AN96" s="1"/>
       <c r="AO96" s="1"/>
       <c r="AP96" s="1"/>
@@ -11857,7 +11864,7 @@
       <c r="AJ97" s="1"/>
       <c r="AK97" s="1"/>
       <c r="AL97" s="1"/>
-      <c r="AM97" s="1"/>
+      <c r="AM97" s="25"/>
       <c r="AN97" s="1"/>
       <c r="AO97" s="1"/>
       <c r="AP97" s="1"/>
@@ -11912,7 +11919,7 @@
       <c r="AJ98" s="1"/>
       <c r="AK98" s="1"/>
       <c r="AL98" s="1"/>
-      <c r="AM98" s="1"/>
+      <c r="AM98" s="25"/>
       <c r="AN98" s="1"/>
       <c r="AO98" s="1"/>
       <c r="AP98" s="1"/>
@@ -11967,7 +11974,7 @@
       <c r="AJ99" s="1"/>
       <c r="AK99" s="1"/>
       <c r="AL99" s="1"/>
-      <c r="AM99" s="1"/>
+      <c r="AM99" s="25"/>
       <c r="AN99" s="1"/>
       <c r="AO99" s="1"/>
       <c r="AP99" s="1"/>
@@ -12022,7 +12029,7 @@
       <c r="AJ100" s="1"/>
       <c r="AK100" s="1"/>
       <c r="AL100" s="1"/>
-      <c r="AM100" s="1"/>
+      <c r="AM100" s="25"/>
       <c r="AN100" s="1"/>
       <c r="AO100" s="1"/>
       <c r="AP100" s="1"/>
@@ -12077,7 +12084,7 @@
       <c r="AJ101" s="1"/>
       <c r="AK101" s="1"/>
       <c r="AL101" s="1"/>
-      <c r="AM101" s="1"/>
+      <c r="AM101" s="25"/>
       <c r="AN101" s="1"/>
       <c r="AO101" s="1"/>
       <c r="AP101" s="1"/>
@@ -12132,7 +12139,7 @@
       <c r="AJ102" s="1"/>
       <c r="AK102" s="1"/>
       <c r="AL102" s="1"/>
-      <c r="AM102" s="1"/>
+      <c r="AM102" s="25"/>
       <c r="AN102" s="1"/>
       <c r="AO102" s="1"/>
       <c r="AP102" s="1"/>
@@ -12187,7 +12194,7 @@
       <c r="AJ103" s="1"/>
       <c r="AK103" s="1"/>
       <c r="AL103" s="1"/>
-      <c r="AM103" s="1"/>
+      <c r="AM103" s="25"/>
       <c r="AN103" s="1"/>
       <c r="AO103" s="1"/>
       <c r="AP103" s="1"/>
@@ -12242,7 +12249,7 @@
       <c r="AJ104" s="1"/>
       <c r="AK104" s="1"/>
       <c r="AL104" s="1"/>
-      <c r="AM104" s="1"/>
+      <c r="AM104" s="25"/>
       <c r="AN104" s="1"/>
       <c r="AO104" s="1"/>
       <c r="AP104" s="1"/>
@@ -12297,7 +12304,7 @@
       <c r="AJ105" s="1"/>
       <c r="AK105" s="1"/>
       <c r="AL105" s="1"/>
-      <c r="AM105" s="1"/>
+      <c r="AM105" s="25"/>
       <c r="AN105" s="1"/>
       <c r="AO105" s="1"/>
       <c r="AP105" s="1"/>
@@ -12352,7 +12359,7 @@
       <c r="AJ106" s="1"/>
       <c r="AK106" s="1"/>
       <c r="AL106" s="1"/>
-      <c r="AM106" s="1"/>
+      <c r="AM106" s="25"/>
       <c r="AN106" s="1"/>
       <c r="AO106" s="1"/>
       <c r="AP106" s="1"/>
@@ -12407,7 +12414,7 @@
       <c r="AJ107" s="1"/>
       <c r="AK107" s="1"/>
       <c r="AL107" s="1"/>
-      <c r="AM107" s="1"/>
+      <c r="AM107" s="25"/>
       <c r="AN107" s="1"/>
       <c r="AO107" s="1"/>
       <c r="AP107" s="1"/>
@@ -12462,7 +12469,7 @@
       <c r="AJ108" s="1"/>
       <c r="AK108" s="1"/>
       <c r="AL108" s="1"/>
-      <c r="AM108" s="1"/>
+      <c r="AM108" s="25"/>
       <c r="AN108" s="1"/>
       <c r="AO108" s="1"/>
       <c r="AP108" s="1"/>
@@ -12517,7 +12524,7 @@
       <c r="AJ109" s="1"/>
       <c r="AK109" s="1"/>
       <c r="AL109" s="1"/>
-      <c r="AM109" s="1"/>
+      <c r="AM109" s="25"/>
       <c r="AN109" s="1"/>
       <c r="AO109" s="1"/>
       <c r="AP109" s="1"/>
@@ -12572,7 +12579,7 @@
       <c r="AJ110" s="1"/>
       <c r="AK110" s="1"/>
       <c r="AL110" s="1"/>
-      <c r="AM110" s="1"/>
+      <c r="AM110" s="25"/>
       <c r="AN110" s="1"/>
       <c r="AO110" s="1"/>
       <c r="AP110" s="1"/>
@@ -12627,7 +12634,7 @@
       <c r="AJ111" s="1"/>
       <c r="AK111" s="1"/>
       <c r="AL111" s="1"/>
-      <c r="AM111" s="1"/>
+      <c r="AM111" s="25"/>
       <c r="AN111" s="1"/>
       <c r="AO111" s="1"/>
       <c r="AP111" s="1"/>
@@ -12682,7 +12689,7 @@
       <c r="AJ112" s="1"/>
       <c r="AK112" s="1"/>
       <c r="AL112" s="1"/>
-      <c r="AM112" s="1"/>
+      <c r="AM112" s="25"/>
       <c r="AN112" s="1"/>
       <c r="AO112" s="1"/>
       <c r="AP112" s="1"/>
@@ -12737,7 +12744,7 @@
       <c r="AJ113" s="1"/>
       <c r="AK113" s="1"/>
       <c r="AL113" s="1"/>
-      <c r="AM113" s="1"/>
+      <c r="AM113" s="25"/>
       <c r="AN113" s="1"/>
       <c r="AO113" s="1"/>
       <c r="AP113" s="1"/>
@@ -12792,7 +12799,7 @@
       <c r="AJ114" s="1"/>
       <c r="AK114" s="1"/>
       <c r="AL114" s="1"/>
-      <c r="AM114" s="1"/>
+      <c r="AM114" s="25"/>
       <c r="AN114" s="1"/>
       <c r="AO114" s="1"/>
       <c r="AP114" s="1"/>
@@ -12847,7 +12854,7 @@
       <c r="AJ115" s="1"/>
       <c r="AK115" s="1"/>
       <c r="AL115" s="1"/>
-      <c r="AM115" s="1"/>
+      <c r="AM115" s="25"/>
       <c r="AN115" s="1"/>
       <c r="AO115" s="1"/>
       <c r="AP115" s="1"/>
@@ -12902,7 +12909,7 @@
       <c r="AJ116" s="1"/>
       <c r="AK116" s="1"/>
       <c r="AL116" s="1"/>
-      <c r="AM116" s="1"/>
+      <c r="AM116" s="25"/>
       <c r="AN116" s="1"/>
       <c r="AO116" s="1"/>
       <c r="AP116" s="1"/>
@@ -12957,7 +12964,7 @@
       <c r="AJ117" s="1"/>
       <c r="AK117" s="1"/>
       <c r="AL117" s="1"/>
-      <c r="AM117" s="1"/>
+      <c r="AM117" s="25"/>
       <c r="AN117" s="1"/>
       <c r="AO117" s="1"/>
       <c r="AP117" s="1"/>
@@ -13012,7 +13019,7 @@
       <c r="AJ118" s="1"/>
       <c r="AK118" s="1"/>
       <c r="AL118" s="1"/>
-      <c r="AM118" s="1"/>
+      <c r="AM118" s="25"/>
       <c r="AN118" s="1"/>
       <c r="AO118" s="1"/>
       <c r="AP118" s="1"/>
@@ -13067,7 +13074,7 @@
       <c r="AJ119" s="1"/>
       <c r="AK119" s="1"/>
       <c r="AL119" s="1"/>
-      <c r="AM119" s="1"/>
+      <c r="AM119" s="25"/>
       <c r="AN119" s="1"/>
       <c r="AO119" s="1"/>
       <c r="AP119" s="1"/>
@@ -13122,7 +13129,7 @@
       <c r="AJ120" s="1"/>
       <c r="AK120" s="1"/>
       <c r="AL120" s="1"/>
-      <c r="AM120" s="1"/>
+      <c r="AM120" s="25"/>
       <c r="AN120" s="1"/>
       <c r="AO120" s="1"/>
       <c r="AP120" s="1"/>
@@ -13177,7 +13184,7 @@
       <c r="AJ121" s="1"/>
       <c r="AK121" s="1"/>
       <c r="AL121" s="1"/>
-      <c r="AM121" s="1"/>
+      <c r="AM121" s="25"/>
       <c r="AN121" s="1"/>
       <c r="AO121" s="1"/>
       <c r="AP121" s="1"/>
@@ -13232,7 +13239,7 @@
       <c r="AJ122" s="1"/>
       <c r="AK122" s="1"/>
       <c r="AL122" s="1"/>
-      <c r="AM122" s="1"/>
+      <c r="AM122" s="25"/>
       <c r="AN122" s="1"/>
       <c r="AO122" s="1"/>
       <c r="AP122" s="1"/>
@@ -13287,7 +13294,7 @@
       <c r="AJ123" s="1"/>
       <c r="AK123" s="1"/>
       <c r="AL123" s="1"/>
-      <c r="AM123" s="1"/>
+      <c r="AM123" s="25"/>
       <c r="AN123" s="1"/>
       <c r="AO123" s="1"/>
       <c r="AP123" s="1"/>
@@ -13342,7 +13349,7 @@
       <c r="AJ124" s="1"/>
       <c r="AK124" s="1"/>
       <c r="AL124" s="1"/>
-      <c r="AM124" s="1"/>
+      <c r="AM124" s="25"/>
       <c r="AN124" s="1"/>
       <c r="AO124" s="1"/>
       <c r="AP124" s="1"/>
@@ -13397,7 +13404,7 @@
       <c r="AJ125" s="1"/>
       <c r="AK125" s="1"/>
       <c r="AL125" s="1"/>
-      <c r="AM125" s="1"/>
+      <c r="AM125" s="25"/>
       <c r="AN125" s="1"/>
       <c r="AO125" s="1"/>
       <c r="AP125" s="1"/>
@@ -13452,7 +13459,7 @@
       <c r="AJ126" s="1"/>
       <c r="AK126" s="1"/>
       <c r="AL126" s="1"/>
-      <c r="AM126" s="1"/>
+      <c r="AM126" s="25"/>
       <c r="AN126" s="1"/>
       <c r="AO126" s="1"/>
       <c r="AP126" s="1"/>
@@ -13507,7 +13514,7 @@
       <c r="AJ127" s="1"/>
       <c r="AK127" s="1"/>
       <c r="AL127" s="1"/>
-      <c r="AM127" s="1"/>
+      <c r="AM127" s="25"/>
       <c r="AN127" s="1"/>
       <c r="AO127" s="1"/>
       <c r="AP127" s="1"/>
@@ -13562,7 +13569,7 @@
       <c r="AJ128" s="1"/>
       <c r="AK128" s="1"/>
       <c r="AL128" s="1"/>
-      <c r="AM128" s="1"/>
+      <c r="AM128" s="25"/>
       <c r="AN128" s="1"/>
       <c r="AO128" s="1"/>
       <c r="AP128" s="1"/>
@@ -13617,7 +13624,7 @@
       <c r="AJ129" s="1"/>
       <c r="AK129" s="1"/>
       <c r="AL129" s="1"/>
-      <c r="AM129" s="1"/>
+      <c r="AM129" s="25"/>
       <c r="AN129" s="1"/>
       <c r="AO129" s="1"/>
       <c r="AP129" s="1"/>
@@ -13672,7 +13679,7 @@
       <c r="AJ130" s="1"/>
       <c r="AK130" s="1"/>
       <c r="AL130" s="1"/>
-      <c r="AM130" s="1"/>
+      <c r="AM130" s="25"/>
       <c r="AN130" s="1"/>
       <c r="AO130" s="1"/>
       <c r="AP130" s="1"/>
@@ -13727,7 +13734,7 @@
       <c r="AJ131" s="1"/>
       <c r="AK131" s="1"/>
       <c r="AL131" s="1"/>
-      <c r="AM131" s="1"/>
+      <c r="AM131" s="25"/>
       <c r="AN131" s="1"/>
       <c r="AO131" s="1"/>
       <c r="AP131" s="1"/>
@@ -13782,7 +13789,7 @@
       <c r="AJ132" s="1"/>
       <c r="AK132" s="1"/>
       <c r="AL132" s="1"/>
-      <c r="AM132" s="1"/>
+      <c r="AM132" s="25"/>
       <c r="AN132" s="1"/>
       <c r="AO132" s="1"/>
       <c r="AP132" s="1"/>
@@ -13837,7 +13844,7 @@
       <c r="AJ133" s="1"/>
       <c r="AK133" s="1"/>
       <c r="AL133" s="1"/>
-      <c r="AM133" s="1"/>
+      <c r="AM133" s="25"/>
       <c r="AN133" s="1"/>
       <c r="AO133" s="1"/>
       <c r="AP133" s="1"/>
@@ -13892,7 +13899,7 @@
       <c r="AJ134" s="1"/>
       <c r="AK134" s="1"/>
       <c r="AL134" s="1"/>
-      <c r="AM134" s="1"/>
+      <c r="AM134" s="25"/>
       <c r="AN134" s="1"/>
       <c r="AO134" s="1"/>
       <c r="AP134" s="1"/>
@@ -13947,7 +13954,7 @@
       <c r="AJ135" s="1"/>
       <c r="AK135" s="1"/>
       <c r="AL135" s="1"/>
-      <c r="AM135" s="1"/>
+      <c r="AM135" s="25"/>
       <c r="AN135" s="1"/>
       <c r="AO135" s="1"/>
       <c r="AP135" s="1"/>
@@ -14002,7 +14009,7 @@
       <c r="AJ136" s="1"/>
       <c r="AK136" s="1"/>
       <c r="AL136" s="1"/>
-      <c r="AM136" s="1"/>
+      <c r="AM136" s="25"/>
       <c r="AN136" s="1"/>
       <c r="AO136" s="1"/>
       <c r="AP136" s="1"/>
@@ -14057,7 +14064,7 @@
       <c r="AJ137" s="1"/>
       <c r="AK137" s="1"/>
       <c r="AL137" s="1"/>
-      <c r="AM137" s="1"/>
+      <c r="AM137" s="25"/>
       <c r="AN137" s="1"/>
       <c r="AO137" s="1"/>
       <c r="AP137" s="1"/>
@@ -14112,7 +14119,7 @@
       <c r="AJ138" s="1"/>
       <c r="AK138" s="1"/>
       <c r="AL138" s="1"/>
-      <c r="AM138" s="1"/>
+      <c r="AM138" s="25"/>
       <c r="AN138" s="1"/>
       <c r="AO138" s="1"/>
       <c r="AP138" s="1"/>
@@ -14167,7 +14174,7 @@
       <c r="AJ139" s="1"/>
       <c r="AK139" s="1"/>
       <c r="AL139" s="1"/>
-      <c r="AM139" s="1"/>
+      <c r="AM139" s="25"/>
       <c r="AN139" s="1"/>
       <c r="AO139" s="1"/>
       <c r="AP139" s="1"/>
@@ -14222,7 +14229,7 @@
       <c r="AJ140" s="1"/>
       <c r="AK140" s="1"/>
       <c r="AL140" s="1"/>
-      <c r="AM140" s="1"/>
+      <c r="AM140" s="25"/>
       <c r="AN140" s="1"/>
       <c r="AO140" s="1"/>
       <c r="AP140" s="1"/>
@@ -14277,7 +14284,7 @@
       <c r="AJ141" s="1"/>
       <c r="AK141" s="1"/>
       <c r="AL141" s="1"/>
-      <c r="AM141" s="1"/>
+      <c r="AM141" s="25"/>
       <c r="AN141" s="1"/>
       <c r="AO141" s="1"/>
       <c r="AP141" s="1"/>
@@ -14332,7 +14339,7 @@
       <c r="AJ142" s="1"/>
       <c r="AK142" s="1"/>
       <c r="AL142" s="1"/>
-      <c r="AM142" s="1"/>
+      <c r="AM142" s="25"/>
       <c r="AN142" s="1"/>
       <c r="AO142" s="1"/>
       <c r="AP142" s="1"/>
@@ -14387,7 +14394,7 @@
       <c r="AJ143" s="1"/>
       <c r="AK143" s="1"/>
       <c r="AL143" s="1"/>
-      <c r="AM143" s="1"/>
+      <c r="AM143" s="25"/>
       <c r="AN143" s="1"/>
       <c r="AO143" s="1"/>
       <c r="AP143" s="1"/>
@@ -14442,7 +14449,7 @@
       <c r="AJ144" s="1"/>
       <c r="AK144" s="1"/>
       <c r="AL144" s="1"/>
-      <c r="AM144" s="1"/>
+      <c r="AM144" s="25"/>
       <c r="AN144" s="1"/>
       <c r="AO144" s="1"/>
       <c r="AP144" s="1"/>
@@ -14497,7 +14504,7 @@
       <c r="AJ145" s="1"/>
       <c r="AK145" s="1"/>
       <c r="AL145" s="1"/>
-      <c r="AM145" s="1"/>
+      <c r="AM145" s="25"/>
       <c r="AN145" s="1"/>
       <c r="AO145" s="1"/>
       <c r="AP145" s="1"/>
@@ -14552,7 +14559,7 @@
       <c r="AJ146" s="1"/>
       <c r="AK146" s="1"/>
       <c r="AL146" s="1"/>
-      <c r="AM146" s="1"/>
+      <c r="AM146" s="25"/>
       <c r="AN146" s="1"/>
       <c r="AO146" s="1"/>
       <c r="AP146" s="1"/>
@@ -14607,7 +14614,7 @@
       <c r="AJ147" s="1"/>
       <c r="AK147" s="1"/>
       <c r="AL147" s="1"/>
-      <c r="AM147" s="1"/>
+      <c r="AM147" s="25"/>
       <c r="AN147" s="1"/>
       <c r="AO147" s="1"/>
       <c r="AP147" s="1"/>
@@ -14662,7 +14669,7 @@
       <c r="AJ148" s="1"/>
       <c r="AK148" s="1"/>
       <c r="AL148" s="1"/>
-      <c r="AM148" s="1"/>
+      <c r="AM148" s="25"/>
       <c r="AN148" s="1"/>
       <c r="AO148" s="1"/>
       <c r="AP148" s="1"/>
@@ -14717,7 +14724,7 @@
       <c r="AJ149" s="1"/>
       <c r="AK149" s="1"/>
       <c r="AL149" s="1"/>
-      <c r="AM149" s="1"/>
+      <c r="AM149" s="25"/>
       <c r="AN149" s="1"/>
       <c r="AO149" s="1"/>
       <c r="AP149" s="1"/>
@@ -14772,7 +14779,7 @@
       <c r="AJ150" s="1"/>
       <c r="AK150" s="1"/>
       <c r="AL150" s="1"/>
-      <c r="AM150" s="1"/>
+      <c r="AM150" s="25"/>
       <c r="AN150" s="1"/>
       <c r="AO150" s="1"/>
       <c r="AP150" s="1"/>
@@ -14827,7 +14834,7 @@
       <c r="AJ151" s="1"/>
       <c r="AK151" s="1"/>
       <c r="AL151" s="1"/>
-      <c r="AM151" s="1"/>
+      <c r="AM151" s="25"/>
       <c r="AN151" s="1"/>
       <c r="AO151" s="1"/>
       <c r="AP151" s="1"/>
@@ -14882,7 +14889,7 @@
       <c r="AJ152" s="1"/>
       <c r="AK152" s="1"/>
       <c r="AL152" s="1"/>
-      <c r="AM152" s="1"/>
+      <c r="AM152" s="25"/>
       <c r="AN152" s="1"/>
       <c r="AO152" s="1"/>
       <c r="AP152" s="1"/>
@@ -14937,7 +14944,7 @@
       <c r="AJ153" s="1"/>
       <c r="AK153" s="1"/>
       <c r="AL153" s="1"/>
-      <c r="AM153" s="1"/>
+      <c r="AM153" s="25"/>
       <c r="AN153" s="1"/>
       <c r="AO153" s="1"/>
       <c r="AP153" s="1"/>
@@ -14992,7 +14999,7 @@
       <c r="AJ154" s="1"/>
       <c r="AK154" s="1"/>
       <c r="AL154" s="1"/>
-      <c r="AM154" s="1"/>
+      <c r="AM154" s="25"/>
       <c r="AN154" s="1"/>
       <c r="AO154" s="1"/>
       <c r="AP154" s="1"/>
@@ -15047,7 +15054,7 @@
       <c r="AJ155" s="1"/>
       <c r="AK155" s="1"/>
       <c r="AL155" s="1"/>
-      <c r="AM155" s="1"/>
+      <c r="AM155" s="25"/>
       <c r="AN155" s="1"/>
       <c r="AO155" s="1"/>
       <c r="AP155" s="1"/>
@@ -15102,7 +15109,7 @@
       <c r="AJ156" s="1"/>
       <c r="AK156" s="1"/>
       <c r="AL156" s="1"/>
-      <c r="AM156" s="1"/>
+      <c r="AM156" s="25"/>
       <c r="AN156" s="1"/>
       <c r="AO156" s="1"/>
       <c r="AP156" s="1"/>
@@ -15157,7 +15164,7 @@
       <c r="AJ157" s="1"/>
       <c r="AK157" s="1"/>
       <c r="AL157" s="1"/>
-      <c r="AM157" s="1"/>
+      <c r="AM157" s="25"/>
       <c r="AN157" s="1"/>
       <c r="AO157" s="1"/>
       <c r="AP157" s="1"/>
@@ -15212,7 +15219,7 @@
       <c r="AJ158" s="1"/>
       <c r="AK158" s="1"/>
       <c r="AL158" s="1"/>
-      <c r="AM158" s="1"/>
+      <c r="AM158" s="25"/>
       <c r="AN158" s="1"/>
       <c r="AO158" s="1"/>
       <c r="AP158" s="1"/>
@@ -15267,7 +15274,7 @@
       <c r="AJ159" s="1"/>
       <c r="AK159" s="1"/>
       <c r="AL159" s="1"/>
-      <c r="AM159" s="1"/>
+      <c r="AM159" s="25"/>
       <c r="AN159" s="1"/>
       <c r="AO159" s="1"/>
       <c r="AP159" s="1"/>
@@ -15322,7 +15329,7 @@
       <c r="AJ160" s="1"/>
       <c r="AK160" s="1"/>
       <c r="AL160" s="1"/>
-      <c r="AM160" s="1"/>
+      <c r="AM160" s="25"/>
       <c r="AN160" s="1"/>
       <c r="AO160" s="1"/>
       <c r="AP160" s="1"/>
@@ -15377,7 +15384,7 @@
       <c r="AJ161" s="1"/>
       <c r="AK161" s="1"/>
       <c r="AL161" s="1"/>
-      <c r="AM161" s="1"/>
+      <c r="AM161" s="25"/>
       <c r="AN161" s="1"/>
       <c r="AO161" s="1"/>
       <c r="AP161" s="1"/>
@@ -15432,7 +15439,7 @@
       <c r="AJ162" s="1"/>
       <c r="AK162" s="1"/>
       <c r="AL162" s="1"/>
-      <c r="AM162" s="1"/>
+      <c r="AM162" s="25"/>
       <c r="AN162" s="1"/>
       <c r="AO162" s="1"/>
       <c r="AP162" s="1"/>
@@ -15487,7 +15494,7 @@
       <c r="AJ163" s="1"/>
       <c r="AK163" s="1"/>
       <c r="AL163" s="1"/>
-      <c r="AM163" s="1"/>
+      <c r="AM163" s="25"/>
       <c r="AN163" s="1"/>
       <c r="AO163" s="1"/>
       <c r="AP163" s="1"/>
@@ -15542,7 +15549,7 @@
       <c r="AJ164" s="1"/>
       <c r="AK164" s="1"/>
       <c r="AL164" s="1"/>
-      <c r="AM164" s="1"/>
+      <c r="AM164" s="25"/>
       <c r="AN164" s="1"/>
       <c r="AO164" s="1"/>
       <c r="AP164" s="1"/>
@@ -15597,7 +15604,7 @@
       <c r="AJ165" s="1"/>
       <c r="AK165" s="1"/>
       <c r="AL165" s="1"/>
-      <c r="AM165" s="1"/>
+      <c r="AM165" s="25"/>
       <c r="AN165" s="1"/>
       <c r="AO165" s="1"/>
       <c r="AP165" s="1"/>
@@ -15652,7 +15659,7 @@
       <c r="AJ166" s="1"/>
       <c r="AK166" s="1"/>
       <c r="AL166" s="1"/>
-      <c r="AM166" s="1"/>
+      <c r="AM166" s="25"/>
       <c r="AN166" s="1"/>
       <c r="AO166" s="1"/>
       <c r="AP166" s="1"/>
@@ -15707,7 +15714,7 @@
       <c r="AJ167" s="1"/>
       <c r="AK167" s="1"/>
       <c r="AL167" s="1"/>
-      <c r="AM167" s="1"/>
+      <c r="AM167" s="25"/>
       <c r="AN167" s="1"/>
       <c r="AO167" s="1"/>
       <c r="AP167" s="1"/>
@@ -15762,7 +15769,7 @@
       <c r="AJ168" s="1"/>
       <c r="AK168" s="1"/>
       <c r="AL168" s="1"/>
-      <c r="AM168" s="1"/>
+      <c r="AM168" s="25"/>
       <c r="AN168" s="1"/>
       <c r="AO168" s="1"/>
       <c r="AP168" s="1"/>
@@ -15817,7 +15824,7 @@
       <c r="AJ169" s="1"/>
       <c r="AK169" s="1"/>
       <c r="AL169" s="1"/>
-      <c r="AM169" s="1"/>
+      <c r="AM169" s="25"/>
       <c r="AN169" s="1"/>
       <c r="AO169" s="1"/>
       <c r="AP169" s="1"/>
@@ -15872,7 +15879,7 @@
       <c r="AJ170" s="1"/>
       <c r="AK170" s="1"/>
       <c r="AL170" s="1"/>
-      <c r="AM170" s="1"/>
+      <c r="AM170" s="25"/>
       <c r="AN170" s="1"/>
       <c r="AO170" s="1"/>
       <c r="AP170" s="1"/>
@@ -15927,7 +15934,7 @@
       <c r="AJ171" s="1"/>
       <c r="AK171" s="1"/>
       <c r="AL171" s="1"/>
-      <c r="AM171" s="1"/>
+      <c r="AM171" s="25"/>
       <c r="AN171" s="1"/>
       <c r="AO171" s="1"/>
       <c r="AP171" s="1"/>
@@ -15982,7 +15989,7 @@
       <c r="AJ172" s="1"/>
       <c r="AK172" s="1"/>
       <c r="AL172" s="1"/>
-      <c r="AM172" s="1"/>
+      <c r="AM172" s="25"/>
       <c r="AN172" s="1"/>
       <c r="AO172" s="1"/>
       <c r="AP172" s="1"/>
@@ -16037,7 +16044,7 @@
       <c r="AJ173" s="1"/>
       <c r="AK173" s="1"/>
       <c r="AL173" s="1"/>
-      <c r="AM173" s="1"/>
+      <c r="AM173" s="25"/>
       <c r="AN173" s="1"/>
       <c r="AO173" s="1"/>
       <c r="AP173" s="1"/>
@@ -16092,7 +16099,7 @@
       <c r="AJ174" s="1"/>
       <c r="AK174" s="1"/>
       <c r="AL174" s="1"/>
-      <c r="AM174" s="1"/>
+      <c r="AM174" s="25"/>
       <c r="AN174" s="1"/>
       <c r="AO174" s="1"/>
       <c r="AP174" s="1"/>
@@ -16147,7 +16154,7 @@
       <c r="AJ175" s="1"/>
       <c r="AK175" s="1"/>
       <c r="AL175" s="1"/>
-      <c r="AM175" s="1"/>
+      <c r="AM175" s="25"/>
       <c r="AN175" s="1"/>
       <c r="AO175" s="1"/>
       <c r="AP175" s="1"/>
@@ -16202,7 +16209,7 @@
       <c r="AJ176" s="1"/>
       <c r="AK176" s="1"/>
       <c r="AL176" s="1"/>
-      <c r="AM176" s="1"/>
+      <c r="AM176" s="25"/>
       <c r="AN176" s="1"/>
       <c r="AO176" s="1"/>
       <c r="AP176" s="1"/>
@@ -16257,7 +16264,7 @@
       <c r="AJ177" s="1"/>
       <c r="AK177" s="1"/>
       <c r="AL177" s="1"/>
-      <c r="AM177" s="1"/>
+      <c r="AM177" s="25"/>
       <c r="AN177" s="1"/>
       <c r="AO177" s="1"/>
       <c r="AP177" s="1"/>
@@ -16312,7 +16319,7 @@
       <c r="AJ178" s="1"/>
       <c r="AK178" s="1"/>
       <c r="AL178" s="1"/>
-      <c r="AM178" s="1"/>
+      <c r="AM178" s="25"/>
       <c r="AN178" s="1"/>
       <c r="AO178" s="1"/>
       <c r="AP178" s="1"/>
@@ -16367,7 +16374,7 @@
       <c r="AJ179" s="1"/>
       <c r="AK179" s="1"/>
       <c r="AL179" s="1"/>
-      <c r="AM179" s="1"/>
+      <c r="AM179" s="25"/>
       <c r="AN179" s="1"/>
       <c r="AO179" s="1"/>
       <c r="AP179" s="1"/>
@@ -16422,7 +16429,7 @@
       <c r="AJ180" s="1"/>
       <c r="AK180" s="1"/>
       <c r="AL180" s="1"/>
-      <c r="AM180" s="1"/>
+      <c r="AM180" s="25"/>
       <c r="AN180" s="1"/>
       <c r="AO180" s="1"/>
       <c r="AP180" s="1"/>
@@ -16477,7 +16484,7 @@
       <c r="AJ181" s="1"/>
       <c r="AK181" s="1"/>
       <c r="AL181" s="1"/>
-      <c r="AM181" s="1"/>
+      <c r="AM181" s="25"/>
       <c r="AN181" s="1"/>
       <c r="AO181" s="1"/>
       <c r="AP181" s="1"/>
@@ -16532,7 +16539,7 @@
       <c r="AJ182" s="1"/>
       <c r="AK182" s="1"/>
       <c r="AL182" s="1"/>
-      <c r="AM182" s="1"/>
+      <c r="AM182" s="25"/>
       <c r="AN182" s="1"/>
       <c r="AO182" s="1"/>
       <c r="AP182" s="1"/>
@@ -16587,7 +16594,7 @@
       <c r="AJ183" s="1"/>
       <c r="AK183" s="1"/>
       <c r="AL183" s="1"/>
-      <c r="AM183" s="1"/>
+      <c r="AM183" s="25"/>
       <c r="AN183" s="1"/>
       <c r="AO183" s="1"/>
       <c r="AP183" s="1"/>
@@ -16642,7 +16649,7 @@
       <c r="AJ184" s="1"/>
       <c r="AK184" s="1"/>
       <c r="AL184" s="1"/>
-      <c r="AM184" s="1"/>
+      <c r="AM184" s="25"/>
       <c r="AN184" s="1"/>
       <c r="AO184" s="1"/>
       <c r="AP184" s="1"/>
@@ -16697,7 +16704,7 @@
       <c r="AJ185" s="1"/>
       <c r="AK185" s="1"/>
       <c r="AL185" s="1"/>
-      <c r="AM185" s="1"/>
+      <c r="AM185" s="25"/>
       <c r="AN185" s="1"/>
       <c r="AO185" s="1"/>
       <c r="AP185" s="1"/>
@@ -16752,7 +16759,7 @@
       <c r="AJ186" s="1"/>
       <c r="AK186" s="1"/>
       <c r="AL186" s="1"/>
-      <c r="AM186" s="1"/>
+      <c r="AM186" s="25"/>
       <c r="AN186" s="1"/>
       <c r="AO186" s="1"/>
       <c r="AP186" s="1"/>
@@ -16807,7 +16814,7 @@
       <c r="AJ187" s="1"/>
       <c r="AK187" s="1"/>
       <c r="AL187" s="1"/>
-      <c r="AM187" s="1"/>
+      <c r="AM187" s="25"/>
       <c r="AN187" s="1"/>
       <c r="AO187" s="1"/>
       <c r="AP187" s="1"/>
@@ -16862,7 +16869,7 @@
       <c r="AJ188" s="1"/>
       <c r="AK188" s="1"/>
       <c r="AL188" s="1"/>
-      <c r="AM188" s="1"/>
+      <c r="AM188" s="25"/>
       <c r="AN188" s="1"/>
       <c r="AO188" s="1"/>
       <c r="AP188" s="1"/>
@@ -16917,7 +16924,7 @@
       <c r="AJ189" s="1"/>
       <c r="AK189" s="1"/>
       <c r="AL189" s="1"/>
-      <c r="AM189" s="1"/>
+      <c r="AM189" s="25"/>
       <c r="AN189" s="1"/>
       <c r="AO189" s="1"/>
       <c r="AP189" s="1"/>
@@ -16972,7 +16979,7 @@
       <c r="AJ190" s="1"/>
       <c r="AK190" s="1"/>
       <c r="AL190" s="1"/>
-      <c r="AM190" s="1"/>
+      <c r="AM190" s="25"/>
       <c r="AN190" s="1"/>
       <c r="AO190" s="1"/>
       <c r="AP190" s="1"/>
@@ -17027,7 +17034,7 @@
       <c r="AJ191" s="1"/>
       <c r="AK191" s="1"/>
       <c r="AL191" s="1"/>
-      <c r="AM191" s="1"/>
+      <c r="AM191" s="25"/>
       <c r="AN191" s="1"/>
       <c r="AO191" s="1"/>
       <c r="AP191" s="1"/>
@@ -17082,7 +17089,7 @@
       <c r="AJ192" s="1"/>
       <c r="AK192" s="1"/>
       <c r="AL192" s="1"/>
-      <c r="AM192" s="1"/>
+      <c r="AM192" s="25"/>
       <c r="AN192" s="1"/>
       <c r="AO192" s="1"/>
       <c r="AP192" s="1"/>
@@ -17137,7 +17144,7 @@
       <c r="AJ193" s="1"/>
       <c r="AK193" s="1"/>
       <c r="AL193" s="1"/>
-      <c r="AM193" s="1"/>
+      <c r="AM193" s="25"/>
       <c r="AN193" s="1"/>
       <c r="AO193" s="1"/>
       <c r="AP193" s="1"/>
@@ -17192,7 +17199,7 @@
       <c r="AJ194" s="1"/>
       <c r="AK194" s="1"/>
       <c r="AL194" s="1"/>
-      <c r="AM194" s="1"/>
+      <c r="AM194" s="25"/>
       <c r="AN194" s="1"/>
       <c r="AO194" s="1"/>
       <c r="AP194" s="1"/>
@@ -17247,7 +17254,7 @@
       <c r="AJ195" s="1"/>
       <c r="AK195" s="1"/>
       <c r="AL195" s="1"/>
-      <c r="AM195" s="1"/>
+      <c r="AM195" s="25"/>
       <c r="AN195" s="1"/>
       <c r="AO195" s="1"/>
       <c r="AP195" s="1"/>
@@ -17302,7 +17309,7 @@
       <c r="AJ196" s="1"/>
       <c r="AK196" s="1"/>
       <c r="AL196" s="1"/>
-      <c r="AM196" s="1"/>
+      <c r="AM196" s="25"/>
       <c r="AN196" s="1"/>
       <c r="AO196" s="1"/>
       <c r="AP196" s="1"/>
@@ -17357,7 +17364,7 @@
       <c r="AJ197" s="1"/>
       <c r="AK197" s="1"/>
       <c r="AL197" s="1"/>
-      <c r="AM197" s="1"/>
+      <c r="AM197" s="25"/>
       <c r="AN197" s="1"/>
       <c r="AO197" s="1"/>
       <c r="AP197" s="1"/>
@@ -17412,7 +17419,7 @@
       <c r="AJ198" s="1"/>
       <c r="AK198" s="1"/>
       <c r="AL198" s="1"/>
-      <c r="AM198" s="1"/>
+      <c r="AM198" s="25"/>
       <c r="AN198" s="1"/>
       <c r="AO198" s="1"/>
       <c r="AP198" s="1"/>
@@ -17467,7 +17474,7 @@
       <c r="AJ199" s="1"/>
       <c r="AK199" s="1"/>
       <c r="AL199" s="1"/>
-      <c r="AM199" s="1"/>
+      <c r="AM199" s="25"/>
       <c r="AN199" s="1"/>
       <c r="AO199" s="1"/>
       <c r="AP199" s="1"/>
@@ -17522,7 +17529,7 @@
       <c r="AJ200" s="1"/>
       <c r="AK200" s="1"/>
       <c r="AL200" s="1"/>
-      <c r="AM200" s="1"/>
+      <c r="AM200" s="25"/>
       <c r="AN200" s="1"/>
       <c r="AO200" s="1"/>
       <c r="AP200" s="1"/>
@@ -17577,7 +17584,7 @@
       <c r="AJ201" s="1"/>
       <c r="AK201" s="1"/>
       <c r="AL201" s="1"/>
-      <c r="AM201" s="1"/>
+      <c r="AM201" s="25"/>
       <c r="AN201" s="1"/>
       <c r="AO201" s="1"/>
       <c r="AP201" s="1"/>
@@ -17632,7 +17639,7 @@
       <c r="AJ202" s="1"/>
       <c r="AK202" s="1"/>
       <c r="AL202" s="1"/>
-      <c r="AM202" s="1"/>
+      <c r="AM202" s="25"/>
       <c r="AN202" s="1"/>
       <c r="AO202" s="1"/>
       <c r="AP202" s="1"/>
@@ -17687,7 +17694,7 @@
       <c r="AJ203" s="1"/>
       <c r="AK203" s="1"/>
       <c r="AL203" s="1"/>
-      <c r="AM203" s="1"/>
+      <c r="AM203" s="25"/>
       <c r="AN203" s="1"/>
       <c r="AO203" s="1"/>
       <c r="AP203" s="1"/>
@@ -17742,7 +17749,7 @@
       <c r="AJ204" s="1"/>
       <c r="AK204" s="1"/>
       <c r="AL204" s="1"/>
-      <c r="AM204" s="1"/>
+      <c r="AM204" s="25"/>
       <c r="AN204" s="1"/>
       <c r="AO204" s="1"/>
       <c r="AP204" s="1"/>
@@ -17797,7 +17804,7 @@
       <c r="AJ205" s="1"/>
       <c r="AK205" s="1"/>
       <c r="AL205" s="1"/>
-      <c r="AM205" s="1"/>
+      <c r="AM205" s="25"/>
       <c r="AN205" s="1"/>
       <c r="AO205" s="1"/>
       <c r="AP205" s="1"/>
@@ -17852,7 +17859,7 @@
       <c r="AJ206" s="1"/>
       <c r="AK206" s="1"/>
       <c r="AL206" s="1"/>
-      <c r="AM206" s="1"/>
+      <c r="AM206" s="25"/>
       <c r="AN206" s="1"/>
       <c r="AO206" s="1"/>
       <c r="AP206" s="1"/>
@@ -17907,7 +17914,7 @@
       <c r="AJ207" s="1"/>
       <c r="AK207" s="1"/>
       <c r="AL207" s="1"/>
-      <c r="AM207" s="1"/>
+      <c r="AM207" s="25"/>
       <c r="AN207" s="1"/>
       <c r="AO207" s="1"/>
       <c r="AP207" s="1"/>
@@ -17962,7 +17969,7 @@
       <c r="AJ208" s="1"/>
       <c r="AK208" s="1"/>
       <c r="AL208" s="1"/>
-      <c r="AM208" s="1"/>
+      <c r="AM208" s="25"/>
       <c r="AN208" s="1"/>
       <c r="AO208" s="1"/>
       <c r="AP208" s="1"/>
@@ -18017,7 +18024,7 @@
       <c r="AJ209" s="1"/>
       <c r="AK209" s="1"/>
       <c r="AL209" s="1"/>
-      <c r="AM209" s="1"/>
+      <c r="AM209" s="25"/>
       <c r="AN209" s="1"/>
       <c r="AO209" s="1"/>
       <c r="AP209" s="1"/>
@@ -18072,7 +18079,7 @@
       <c r="AJ210" s="1"/>
       <c r="AK210" s="1"/>
       <c r="AL210" s="1"/>
-      <c r="AM210" s="1"/>
+      <c r="AM210" s="25"/>
       <c r="AN210" s="1"/>
       <c r="AO210" s="1"/>
       <c r="AP210" s="1"/>
@@ -18127,7 +18134,7 @@
       <c r="AJ211" s="1"/>
       <c r="AK211" s="1"/>
       <c r="AL211" s="1"/>
-      <c r="AM211" s="1"/>
+      <c r="AM211" s="25"/>
       <c r="AN211" s="1"/>
       <c r="AO211" s="1"/>
       <c r="AP211" s="1"/>
@@ -18182,7 +18189,7 @@
       <c r="AJ212" s="1"/>
       <c r="AK212" s="1"/>
       <c r="AL212" s="1"/>
-      <c r="AM212" s="1"/>
+      <c r="AM212" s="25"/>
       <c r="AN212" s="1"/>
       <c r="AO212" s="1"/>
       <c r="AP212" s="1"/>
@@ -18237,7 +18244,7 @@
       <c r="AJ213" s="1"/>
       <c r="AK213" s="1"/>
       <c r="AL213" s="1"/>
-      <c r="AM213" s="1"/>
+      <c r="AM213" s="25"/>
       <c r="AN213" s="1"/>
       <c r="AO213" s="1"/>
       <c r="AP213" s="1"/>
@@ -18292,7 +18299,7 @@
       <c r="AJ214" s="1"/>
       <c r="AK214" s="1"/>
       <c r="AL214" s="1"/>
-      <c r="AM214" s="1"/>
+      <c r="AM214" s="25"/>
       <c r="AN214" s="1"/>
       <c r="AO214" s="1"/>
       <c r="AP214" s="1"/>
@@ -18347,7 +18354,7 @@
       <c r="AJ215" s="1"/>
       <c r="AK215" s="1"/>
       <c r="AL215" s="1"/>
-      <c r="AM215" s="1"/>
+      <c r="AM215" s="25"/>
       <c r="AN215" s="1"/>
       <c r="AO215" s="1"/>
       <c r="AP215" s="1"/>
@@ -18402,7 +18409,7 @@
       <c r="AJ216" s="1"/>
       <c r="AK216" s="1"/>
       <c r="AL216" s="1"/>
-      <c r="AM216" s="1"/>
+      <c r="AM216" s="25"/>
       <c r="AN216" s="1"/>
       <c r="AO216" s="1"/>
       <c r="AP216" s="1"/>
@@ -18457,7 +18464,7 @@
       <c r="AJ217" s="1"/>
       <c r="AK217" s="1"/>
       <c r="AL217" s="1"/>
-      <c r="AM217" s="1"/>
+      <c r="AM217" s="25"/>
       <c r="AN217" s="1"/>
       <c r="AO217" s="1"/>
       <c r="AP217" s="1"/>
@@ -18512,7 +18519,7 @@
       <c r="AJ218" s="1"/>
       <c r="AK218" s="1"/>
       <c r="AL218" s="1"/>
-      <c r="AM218" s="1"/>
+      <c r="AM218" s="25"/>
       <c r="AN218" s="1"/>
       <c r="AO218" s="1"/>
       <c r="AP218" s="1"/>
@@ -18567,7 +18574,7 @@
       <c r="AJ219" s="1"/>
       <c r="AK219" s="1"/>
       <c r="AL219" s="1"/>
-      <c r="AM219" s="1"/>
+      <c r="AM219" s="25"/>
       <c r="AN219" s="1"/>
       <c r="AO219" s="1"/>
       <c r="AP219" s="1"/>
@@ -18622,7 +18629,7 @@
       <c r="AJ220" s="1"/>
       <c r="AK220" s="1"/>
       <c r="AL220" s="1"/>
-      <c r="AM220" s="1"/>
+      <c r="AM220" s="25"/>
       <c r="AN220" s="1"/>
       <c r="AO220" s="1"/>
       <c r="AP220" s="1"/>
@@ -18677,7 +18684,7 @@
       <c r="AJ221" s="1"/>
       <c r="AK221" s="1"/>
       <c r="AL221" s="1"/>
-      <c r="AM221" s="1"/>
+      <c r="AM221" s="25"/>
       <c r="AN221" s="1"/>
       <c r="AO221" s="1"/>
       <c r="AP221" s="1"/>
@@ -18732,7 +18739,7 @@
       <c r="AJ222" s="1"/>
       <c r="AK222" s="1"/>
       <c r="AL222" s="1"/>
-      <c r="AM222" s="1"/>
+      <c r="AM222" s="25"/>
       <c r="AN222" s="1"/>
       <c r="AO222" s="1"/>
       <c r="AP222" s="1"/>
@@ -18787,7 +18794,7 @@
       <c r="AJ223" s="1"/>
       <c r="AK223" s="1"/>
       <c r="AL223" s="1"/>
-      <c r="AM223" s="1"/>
+      <c r="AM223" s="25"/>
       <c r="AN223" s="1"/>
       <c r="AO223" s="1"/>
       <c r="AP223" s="1"/>
@@ -18842,7 +18849,7 @@
       <c r="AJ224" s="1"/>
       <c r="AK224" s="1"/>
       <c r="AL224" s="1"/>
-      <c r="AM224" s="1"/>
+      <c r="AM224" s="25"/>
       <c r="AN224" s="1"/>
       <c r="AO224" s="1"/>
       <c r="AP224" s="1"/>
@@ -18897,7 +18904,7 @@
       <c r="AJ225" s="1"/>
       <c r="AK225" s="1"/>
       <c r="AL225" s="1"/>
-      <c r="AM225" s="1"/>
+      <c r="AM225" s="25"/>
       <c r="AN225" s="1"/>
       <c r="AO225" s="1"/>
       <c r="AP225" s="1"/>
@@ -18952,7 +18959,7 @@
       <c r="AJ226" s="1"/>
       <c r="AK226" s="1"/>
       <c r="AL226" s="1"/>
-      <c r="AM226" s="1"/>
+      <c r="AM226" s="25"/>
       <c r="AN226" s="1"/>
       <c r="AO226" s="1"/>
       <c r="AP226" s="1"/>
@@ -19007,7 +19014,7 @@
       <c r="AJ227" s="1"/>
       <c r="AK227" s="1"/>
       <c r="AL227" s="1"/>
-      <c r="AM227" s="1"/>
+      <c r="AM227" s="25"/>
       <c r="AN227" s="1"/>
       <c r="AO227" s="1"/>
       <c r="AP227" s="1"/>
@@ -19062,7 +19069,7 @@
       <c r="AJ228" s="1"/>
       <c r="AK228" s="1"/>
       <c r="AL228" s="1"/>
-      <c r="AM228" s="1"/>
+      <c r="AM228" s="25"/>
       <c r="AN228" s="1"/>
       <c r="AO228" s="1"/>
       <c r="AP228" s="1"/>
@@ -19117,7 +19124,7 @@
       <c r="AJ229" s="1"/>
       <c r="AK229" s="1"/>
       <c r="AL229" s="1"/>
-      <c r="AM229" s="1"/>
+      <c r="AM229" s="25"/>
       <c r="AN229" s="1"/>
       <c r="AO229" s="1"/>
       <c r="AP229" s="1"/>
@@ -19172,7 +19179,7 @@
       <c r="AJ230" s="1"/>
       <c r="AK230" s="1"/>
       <c r="AL230" s="1"/>
-      <c r="AM230" s="1"/>
+      <c r="AM230" s="25"/>
       <c r="AN230" s="1"/>
       <c r="AO230" s="1"/>
       <c r="AP230" s="1"/>
@@ -19227,7 +19234,7 @@
       <c r="AJ231" s="1"/>
       <c r="AK231" s="1"/>
       <c r="AL231" s="1"/>
-      <c r="AM231" s="1"/>
+      <c r="AM231" s="25"/>
       <c r="AN231" s="1"/>
       <c r="AO231" s="1"/>
       <c r="AP231" s="1"/>
@@ -19282,7 +19289,7 @@
       <c r="AJ232" s="1"/>
       <c r="AK232" s="1"/>
       <c r="AL232" s="1"/>
-      <c r="AM232" s="1"/>
+      <c r="AM232" s="25"/>
       <c r="AN232" s="1"/>
       <c r="AO232" s="1"/>
       <c r="AP232" s="1"/>
@@ -19337,7 +19344,7 @@
       <c r="AJ233" s="1"/>
       <c r="AK233" s="1"/>
       <c r="AL233" s="1"/>
-      <c r="AM233" s="1"/>
+      <c r="AM233" s="25"/>
       <c r="AN233" s="1"/>
       <c r="AO233" s="1"/>
       <c r="AP233" s="1"/>
@@ -19392,7 +19399,7 @@
       <c r="AJ234" s="1"/>
       <c r="AK234" s="1"/>
       <c r="AL234" s="1"/>
-      <c r="AM234" s="1"/>
+      <c r="AM234" s="25"/>
       <c r="AN234" s="1"/>
       <c r="AO234" s="1"/>
       <c r="AP234" s="1"/>
@@ -19447,7 +19454,7 @@
       <c r="AJ235" s="1"/>
       <c r="AK235" s="1"/>
       <c r="AL235" s="1"/>
-      <c r="AM235" s="1"/>
+      <c r="AM235" s="25"/>
       <c r="AN235" s="1"/>
       <c r="AO235" s="1"/>
       <c r="AP235" s="1"/>
@@ -19502,7 +19509,7 @@
       <c r="AJ236" s="1"/>
       <c r="AK236" s="1"/>
       <c r="AL236" s="1"/>
-      <c r="AM236" s="1"/>
+      <c r="AM236" s="25"/>
       <c r="AN236" s="1"/>
       <c r="AO236" s="1"/>
       <c r="AP236" s="1"/>
@@ -19557,7 +19564,7 @@
       <c r="AJ237" s="1"/>
       <c r="AK237" s="1"/>
       <c r="AL237" s="1"/>
-      <c r="AM237" s="1"/>
+      <c r="AM237" s="25"/>
       <c r="AN237" s="1"/>
       <c r="AO237" s="1"/>
       <c r="AP237" s="1"/>
@@ -19612,7 +19619,7 @@
       <c r="AJ238" s="1"/>
       <c r="AK238" s="1"/>
       <c r="AL238" s="1"/>
-      <c r="AM238" s="1"/>
+      <c r="AM238" s="25"/>
       <c r="AN238" s="1"/>
       <c r="AO238" s="1"/>
       <c r="AP238" s="1"/>
@@ -19667,7 +19674,7 @@
       <c r="AJ239" s="1"/>
       <c r="AK239" s="1"/>
       <c r="AL239" s="1"/>
-      <c r="AM239" s="1"/>
+      <c r="AM239" s="25"/>
       <c r="AN239" s="1"/>
       <c r="AO239" s="1"/>
       <c r="AP239" s="1"/>
@@ -19722,7 +19729,7 @@
       <c r="AJ240" s="1"/>
       <c r="AK240" s="1"/>
       <c r="AL240" s="1"/>
-      <c r="AM240" s="1"/>
+      <c r="AM240" s="25"/>
       <c r="AN240" s="1"/>
       <c r="AO240" s="1"/>
       <c r="AP240" s="1"/>
@@ -19777,7 +19784,7 @@
       <c r="AJ241" s="1"/>
       <c r="AK241" s="1"/>
       <c r="AL241" s="1"/>
-      <c r="AM241" s="1"/>
+      <c r="AM241" s="25"/>
       <c r="AN241" s="1"/>
       <c r="AO241" s="1"/>
       <c r="AP241" s="1"/>
@@ -19832,7 +19839,7 @@
       <c r="AJ242" s="1"/>
       <c r="AK242" s="1"/>
       <c r="AL242" s="1"/>
-      <c r="AM242" s="1"/>
+      <c r="AM242" s="25"/>
       <c r="AN242" s="1"/>
       <c r="AO242" s="1"/>
       <c r="AP242" s="1"/>
@@ -19887,7 +19894,7 @@
       <c r="AJ243" s="1"/>
       <c r="AK243" s="1"/>
       <c r="AL243" s="1"/>
-      <c r="AM243" s="1"/>
+      <c r="AM243" s="25"/>
       <c r="AN243" s="1"/>
       <c r="AO243" s="1"/>
       <c r="AP243" s="1"/>
@@ -19942,7 +19949,7 @@
       <c r="AJ244" s="1"/>
       <c r="AK244" s="1"/>
       <c r="AL244" s="1"/>
-      <c r="AM244" s="1"/>
+      <c r="AM244" s="25"/>
       <c r="AN244" s="1"/>
       <c r="AO244" s="1"/>
       <c r="AP244" s="1"/>
@@ -19997,7 +20004,7 @@
       <c r="AJ245" s="1"/>
       <c r="AK245" s="1"/>
       <c r="AL245" s="1"/>
-      <c r="AM245" s="1"/>
+      <c r="AM245" s="25"/>
       <c r="AN245" s="1"/>
       <c r="AO245" s="1"/>
       <c r="AP245" s="1"/>
@@ -20052,7 +20059,7 @@
       <c r="AJ246" s="1"/>
       <c r="AK246" s="1"/>
       <c r="AL246" s="1"/>
-      <c r="AM246" s="1"/>
+      <c r="AM246" s="25"/>
       <c r="AN246" s="1"/>
       <c r="AO246" s="1"/>
       <c r="AP246" s="1"/>
@@ -20107,7 +20114,7 @@
       <c r="AJ247" s="1"/>
       <c r="AK247" s="1"/>
       <c r="AL247" s="1"/>
-      <c r="AM247" s="1"/>
+      <c r="AM247" s="25"/>
       <c r="AN247" s="1"/>
       <c r="AO247" s="1"/>
       <c r="AP247" s="1"/>
@@ -20162,7 +20169,7 @@
       <c r="AJ248" s="1"/>
       <c r="AK248" s="1"/>
       <c r="AL248" s="1"/>
-      <c r="AM248" s="1"/>
+      <c r="AM248" s="25"/>
       <c r="AN248" s="1"/>
       <c r="AO248" s="1"/>
       <c r="AP248" s="1"/>
@@ -20217,7 +20224,7 @@
       <c r="AJ249" s="1"/>
       <c r="AK249" s="1"/>
       <c r="AL249" s="1"/>
-      <c r="AM249" s="1"/>
+      <c r="AM249" s="25"/>
       <c r="AN249" s="1"/>
       <c r="AO249" s="1"/>
       <c r="AP249" s="1"/>
@@ -20272,7 +20279,7 @@
       <c r="AJ250" s="1"/>
       <c r="AK250" s="1"/>
       <c r="AL250" s="1"/>
-      <c r="AM250" s="1"/>
+      <c r="AM250" s="25"/>
       <c r="AN250" s="1"/>
       <c r="AO250" s="1"/>
       <c r="AP250" s="1"/>
@@ -20327,7 +20334,7 @@
       <c r="AJ251" s="1"/>
       <c r="AK251" s="1"/>
       <c r="AL251" s="1"/>
-      <c r="AM251" s="1"/>
+      <c r="AM251" s="25"/>
       <c r="AN251" s="1"/>
       <c r="AO251" s="1"/>
       <c r="AP251" s="1"/>
@@ -20382,7 +20389,7 @@
       <c r="AJ252" s="1"/>
       <c r="AK252" s="1"/>
       <c r="AL252" s="1"/>
-      <c r="AM252" s="1"/>
+      <c r="AM252" s="25"/>
       <c r="AN252" s="1"/>
       <c r="AO252" s="1"/>
       <c r="AP252" s="1"/>
@@ -20437,7 +20444,7 @@
       <c r="AJ253" s="1"/>
       <c r="AK253" s="1"/>
       <c r="AL253" s="1"/>
-      <c r="AM253" s="1"/>
+      <c r="AM253" s="25"/>
       <c r="AN253" s="1"/>
       <c r="AO253" s="1"/>
       <c r="AP253" s="1"/>
@@ -20492,7 +20499,7 @@
       <c r="AJ254" s="1"/>
       <c r="AK254" s="1"/>
       <c r="AL254" s="1"/>
-      <c r="AM254" s="1"/>
+      <c r="AM254" s="25"/>
       <c r="AN254" s="1"/>
       <c r="AO254" s="1"/>
       <c r="AP254" s="1"/>
@@ -20547,7 +20554,7 @@
       <c r="AJ255" s="1"/>
       <c r="AK255" s="1"/>
       <c r="AL255" s="1"/>
-      <c r="AM255" s="1"/>
+      <c r="AM255" s="25"/>
       <c r="AN255" s="1"/>
       <c r="AO255" s="1"/>
       <c r="AP255" s="1"/>
@@ -20602,7 +20609,7 @@
       <c r="AJ256" s="1"/>
       <c r="AK256" s="1"/>
       <c r="AL256" s="1"/>
-      <c r="AM256" s="1"/>
+      <c r="AM256" s="25"/>
       <c r="AN256" s="1"/>
       <c r="AO256" s="1"/>
       <c r="AP256" s="1"/>
@@ -20657,7 +20664,7 @@
       <c r="AJ257" s="1"/>
       <c r="AK257" s="1"/>
       <c r="AL257" s="1"/>
-      <c r="AM257" s="1"/>
+      <c r="AM257" s="25"/>
       <c r="AN257" s="1"/>
       <c r="AO257" s="1"/>
       <c r="AP257" s="1"/>
@@ -20712,7 +20719,7 @@
       <c r="AJ258" s="1"/>
       <c r="AK258" s="1"/>
       <c r="AL258" s="1"/>
-      <c r="AM258" s="1"/>
+      <c r="AM258" s="25"/>
       <c r="AN258" s="1"/>
       <c r="AO258" s="1"/>
       <c r="AP258" s="1"/>
@@ -20767,7 +20774,7 @@
       <c r="AJ259" s="1"/>
       <c r="AK259" s="1"/>
       <c r="AL259" s="1"/>
-      <c r="AM259" s="1"/>
+      <c r="AM259" s="25"/>
       <c r="AN259" s="1"/>
       <c r="AO259" s="1"/>
       <c r="AP259" s="1"/>
@@ -20822,7 +20829,7 @@
       <c r="AJ260" s="1"/>
       <c r="AK260" s="1"/>
       <c r="AL260" s="1"/>
-      <c r="AM260" s="1"/>
+      <c r="AM260" s="25"/>
       <c r="AN260" s="1"/>
       <c r="AO260" s="1"/>
       <c r="AP260" s="1"/>
@@ -20877,7 +20884,7 @@
       <c r="AJ261" s="1"/>
       <c r="AK261" s="1"/>
       <c r="AL261" s="1"/>
-      <c r="AM261" s="1"/>
+      <c r="AM261" s="25"/>
       <c r="AN261" s="1"/>
       <c r="AO261" s="1"/>
       <c r="AP261" s="1"/>
@@ -20932,7 +20939,7 @@
       <c r="AJ262" s="1"/>
       <c r="AK262" s="1"/>
       <c r="AL262" s="1"/>
-      <c r="AM262" s="1"/>
+      <c r="AM262" s="25"/>
       <c r="AN262" s="1"/>
       <c r="AO262" s="1"/>
       <c r="AP262" s="1"/>
@@ -20987,7 +20994,7 @@
       <c r="AJ263" s="1"/>
       <c r="AK263" s="1"/>
       <c r="AL263" s="1"/>
-      <c r="AM263" s="1"/>
+      <c r="AM263" s="25"/>
       <c r="AN263" s="1"/>
       <c r="AO263" s="1"/>
       <c r="AP263" s="1"/>
@@ -21042,7 +21049,7 @@
       <c r="AJ264" s="1"/>
       <c r="AK264" s="1"/>
       <c r="AL264" s="1"/>
-      <c r="AM264" s="1"/>
+      <c r="AM264" s="25"/>
       <c r="AN264" s="1"/>
       <c r="AO264" s="1"/>
       <c r="AP264" s="1"/>
@@ -21097,7 +21104,7 @@
       <c r="AJ265" s="1"/>
       <c r="AK265" s="1"/>
       <c r="AL265" s="1"/>
-      <c r="AM265" s="1"/>
+      <c r="AM265" s="25"/>
       <c r="AN265" s="1"/>
       <c r="AO265" s="1"/>
       <c r="AP265" s="1"/>
@@ -21152,7 +21159,7 @@
       <c r="AJ266" s="1"/>
       <c r="AK266" s="1"/>
       <c r="AL266" s="1"/>
-      <c r="AM266" s="1"/>
+      <c r="AM266" s="25"/>
       <c r="AN266" s="1"/>
       <c r="AO266" s="1"/>
       <c r="AP266" s="1"/>
@@ -21207,7 +21214,7 @@
       <c r="AJ267" s="1"/>
       <c r="AK267" s="1"/>
       <c r="AL267" s="1"/>
-      <c r="AM267" s="1"/>
+      <c r="AM267" s="25"/>
       <c r="AN267" s="1"/>
       <c r="AO267" s="1"/>
       <c r="AP267" s="1"/>
@@ -21262,7 +21269,7 @@
       <c r="AJ268" s="1"/>
       <c r="AK268" s="1"/>
       <c r="AL268" s="1"/>
-      <c r="AM268" s="1"/>
+      <c r="AM268" s="25"/>
       <c r="AN268" s="1"/>
       <c r="AO268" s="1"/>
       <c r="AP268" s="1"/>
@@ -21317,7 +21324,7 @@
       <c r="AJ269" s="1"/>
       <c r="AK269" s="1"/>
       <c r="AL269" s="1"/>
-      <c r="AM269" s="1"/>
+      <c r="AM269" s="25"/>
       <c r="AN269" s="1"/>
       <c r="AO269" s="1"/>
       <c r="AP269" s="1"/>
@@ -21372,7 +21379,7 @@
       <c r="AJ270" s="1"/>
       <c r="AK270" s="1"/>
       <c r="AL270" s="1"/>
-      <c r="AM270" s="1"/>
+      <c r="AM270" s="25"/>
       <c r="AN270" s="1"/>
       <c r="AO270" s="1"/>
       <c r="AP270" s="1"/>
@@ -21427,7 +21434,7 @@
       <c r="AJ271" s="1"/>
       <c r="AK271" s="1"/>
       <c r="AL271" s="1"/>
-      <c r="AM271" s="1"/>
+      <c r="AM271" s="25"/>
       <c r="AN271" s="1"/>
       <c r="AO271" s="1"/>
       <c r="AP271" s="1"/>
@@ -21482,7 +21489,7 @@
       <c r="AJ272" s="1"/>
       <c r="AK272" s="1"/>
       <c r="AL272" s="1"/>
-      <c r="AM272" s="1"/>
+      <c r="AM272" s="25"/>
       <c r="AN272" s="1"/>
       <c r="AO272" s="1"/>
       <c r="AP272" s="1"/>
@@ -21537,7 +21544,7 @@
       <c r="AJ273" s="1"/>
       <c r="AK273" s="1"/>
       <c r="AL273" s="1"/>
-      <c r="AM273" s="1"/>
+      <c r="AM273" s="25"/>
       <c r="AN273" s="1"/>
       <c r="AO273" s="1"/>
       <c r="AP273" s="1"/>
@@ -21592,7 +21599,7 @@
       <c r="AJ274" s="1"/>
       <c r="AK274" s="1"/>
       <c r="AL274" s="1"/>
-      <c r="AM274" s="1"/>
+      <c r="AM274" s="25"/>
       <c r="AN274" s="1"/>
       <c r="AO274" s="1"/>
       <c r="AP274" s="1"/>
@@ -21647,7 +21654,7 @@
       <c r="AJ275" s="1"/>
       <c r="AK275" s="1"/>
       <c r="AL275" s="1"/>
-      <c r="AM275" s="1"/>
+      <c r="AM275" s="25"/>
       <c r="AN275" s="1"/>
       <c r="AO275" s="1"/>
       <c r="AP275" s="1"/>
@@ -21702,7 +21709,7 @@
       <c r="AJ276" s="1"/>
       <c r="AK276" s="1"/>
       <c r="AL276" s="1"/>
-      <c r="AM276" s="1"/>
+      <c r="AM276" s="25"/>
       <c r="AN276" s="1"/>
       <c r="AO276" s="1"/>
       <c r="AP276" s="1"/>
@@ -21757,7 +21764,7 @@
       <c r="AJ277" s="1"/>
       <c r="AK277" s="1"/>
       <c r="AL277" s="1"/>
-      <c r="AM277" s="1"/>
+      <c r="AM277" s="25"/>
       <c r="AN277" s="1"/>
       <c r="AO277" s="1"/>
       <c r="AP277" s="1"/>
@@ -21812,7 +21819,7 @@
       <c r="AJ278" s="1"/>
       <c r="AK278" s="1"/>
       <c r="AL278" s="1"/>
-      <c r="AM278" s="1"/>
+      <c r="AM278" s="25"/>
       <c r="AN278" s="1"/>
       <c r="AO278" s="1"/>
       <c r="AP278" s="1"/>
@@ -21867,7 +21874,7 @@
       <c r="AJ279" s="1"/>
       <c r="AK279" s="1"/>
       <c r="AL279" s="1"/>
-      <c r="AM279" s="1"/>
+      <c r="AM279" s="25"/>
       <c r="AN279" s="1"/>
       <c r="AO279" s="1"/>
       <c r="AP279" s="1"/>
@@ -21922,7 +21929,7 @@
       <c r="AJ280" s="1"/>
       <c r="AK280" s="1"/>
       <c r="AL280" s="1"/>
-      <c r="AM280" s="1"/>
+      <c r="AM280" s="25"/>
       <c r="AN280" s="1"/>
       <c r="AO280" s="1"/>
       <c r="AP280" s="1"/>
@@ -21977,7 +21984,7 @@
       <c r="AJ281" s="1"/>
       <c r="AK281" s="1"/>
       <c r="AL281" s="1"/>
-      <c r="AM281" s="1"/>
+      <c r="AM281" s="25"/>
       <c r="AN281" s="1"/>
       <c r="AO281" s="1"/>
       <c r="AP281" s="1"/>
@@ -22032,7 +22039,7 @@
       <c r="AJ282" s="1"/>
       <c r="AK282" s="1"/>
       <c r="AL282" s="1"/>
-      <c r="AM282" s="1"/>
+      <c r="AM282" s="25"/>
       <c r="AN282" s="1"/>
       <c r="AO282" s="1"/>
       <c r="AP282" s="1"/>
@@ -22087,7 +22094,7 @@
       <c r="AJ283" s="1"/>
       <c r="AK283" s="1"/>
       <c r="AL283" s="1"/>
-      <c r="AM283" s="1"/>
+      <c r="AM283" s="25"/>
       <c r="AN283" s="1"/>
       <c r="AO283" s="1"/>
       <c r="AP283" s="1"/>
@@ -22142,7 +22149,7 @@
       <c r="AJ284" s="1"/>
       <c r="AK284" s="1"/>
       <c r="AL284" s="1"/>
-      <c r="AM284" s="1"/>
+      <c r="AM284" s="25"/>
       <c r="AN284" s="1"/>
       <c r="AO284" s="1"/>
       <c r="AP284" s="1"/>
@@ -22197,7 +22204,7 @@
       <c r="AJ285" s="1"/>
       <c r="AK285" s="1"/>
       <c r="AL285" s="1"/>
-      <c r="AM285" s="1"/>
+      <c r="AM285" s="25"/>
       <c r="AN285" s="1"/>
       <c r="AO285" s="1"/>
       <c r="AP285" s="1"/>
@@ -22252,7 +22259,7 @@
       <c r="AJ286" s="1"/>
       <c r="AK286" s="1"/>
       <c r="AL286" s="1"/>
-      <c r="AM286" s="1"/>
+      <c r="AM286" s="25"/>
       <c r="AN286" s="1"/>
       <c r="AO286" s="1"/>
       <c r="AP286" s="1"/>
@@ -22307,7 +22314,7 @@
       <c r="AJ287" s="1"/>
       <c r="AK287" s="1"/>
       <c r="AL287" s="1"/>
-      <c r="AM287" s="1"/>
+      <c r="AM287" s="25"/>
       <c r="AN287" s="1"/>
       <c r="AO287" s="1"/>
       <c r="AP287" s="1"/>
@@ -22362,7 +22369,7 @@
       <c r="AJ288" s="1"/>
       <c r="AK288" s="1"/>
       <c r="AL288" s="1"/>
-      <c r="AM288" s="1"/>
+      <c r="AM288" s="25"/>
       <c r="AN288" s="1"/>
       <c r="AO288" s="1"/>
       <c r="AP288" s="1"/>
@@ -22417,7 +22424,7 @@
       <c r="AJ289" s="1"/>
       <c r="AK289" s="1"/>
       <c r="AL289" s="1"/>
-      <c r="AM289" s="1"/>
+      <c r="AM289" s="25"/>
       <c r="AN289" s="1"/>
       <c r="AO289" s="1"/>
       <c r="AP289" s="1"/>
@@ -22472,7 +22479,7 @@
       <c r="AJ290" s="1"/>
       <c r="AK290" s="1"/>
       <c r="AL290" s="1"/>
-      <c r="AM290" s="1"/>
+      <c r="AM290" s="25"/>
       <c r="AN290" s="1"/>
       <c r="AO290" s="1"/>
       <c r="AP290" s="1"/>
@@ -22527,7 +22534,7 @@
       <c r="AJ291" s="1"/>
       <c r="AK291" s="1"/>
       <c r="AL291" s="1"/>
-      <c r="AM291" s="1"/>
+      <c r="AM291" s="25"/>
       <c r="AN291" s="1"/>
       <c r="AO291" s="1"/>
       <c r="AP291" s="1"/>
@@ -22582,7 +22589,7 @@
       <c r="AJ292" s="1"/>
       <c r="AK292" s="1"/>
       <c r="AL292" s="1"/>
-      <c r="AM292" s="1"/>
+      <c r="AM292" s="25"/>
       <c r="AN292" s="1"/>
       <c r="AO292" s="1"/>
       <c r="AP292" s="1"/>
@@ -22637,7 +22644,7 @@
       <c r="AJ293" s="1"/>
       <c r="AK293" s="1"/>
       <c r="AL293" s="1"/>
-      <c r="AM293" s="1"/>
+      <c r="AM293" s="25"/>
       <c r="AN293" s="1"/>
       <c r="AO293" s="1"/>
       <c r="AP293" s="1"/>
@@ -22692,7 +22699,7 @@
       <c r="AJ294" s="1"/>
       <c r="AK294" s="1"/>
       <c r="AL294" s="1"/>
-      <c r="AM294" s="1"/>
+      <c r="AM294" s="25"/>
       <c r="AN294" s="1"/>
       <c r="AO294" s="1"/>
       <c r="AP294" s="1"/>
@@ -22747,7 +22754,7 @@
       <c r="AJ295" s="1"/>
       <c r="AK295" s="1"/>
       <c r="AL295" s="1"/>
-      <c r="AM295" s="1"/>
+      <c r="AM295" s="25"/>
       <c r="AN295" s="1"/>
       <c r="AO295" s="1"/>
       <c r="AP295" s="1"/>
@@ -22802,7 +22809,7 @@
       <c r="AJ296" s="1"/>
       <c r="AK296" s="1"/>
       <c r="AL296" s="1"/>
-      <c r="AM296" s="1"/>
+      <c r="AM296" s="25"/>
       <c r="AN296" s="1"/>
       <c r="AO296" s="1"/>
       <c r="AP296" s="1"/>
@@ -22857,7 +22864,7 @@
       <c r="AJ297" s="1"/>
       <c r="AK297" s="1"/>
       <c r="AL297" s="1"/>
-      <c r="AM297" s="1"/>
+      <c r="AM297" s="25"/>
       <c r="AN297" s="1"/>
       <c r="AO297" s="1"/>
       <c r="AP297" s="1"/>
@@ -22912,7 +22919,7 @@
       <c r="AJ298" s="1"/>
       <c r="AK298" s="1"/>
       <c r="AL298" s="1"/>
-      <c r="AM298" s="1"/>
+      <c r="AM298" s="25"/>
       <c r="AN298" s="1"/>
       <c r="AO298" s="1"/>
       <c r="AP298" s="1"/>
@@ -22967,7 +22974,7 @@
       <c r="AJ299" s="1"/>
       <c r="AK299" s="1"/>
       <c r="AL299" s="1"/>
-      <c r="AM299" s="1"/>
+      <c r="AM299" s="25"/>
       <c r="AN299" s="1"/>
       <c r="AO299" s="1"/>
       <c r="AP299" s="1"/>
@@ -23022,7 +23029,7 @@
       <c r="AJ300" s="1"/>
       <c r="AK300" s="1"/>
       <c r="AL300" s="1"/>
-      <c r="AM300" s="1"/>
+      <c r="AM300" s="25"/>
       <c r="AN300" s="1"/>
       <c r="AO300" s="1"/>
       <c r="AP300" s="1"/>
@@ -23077,7 +23084,7 @@
       <c r="AJ301" s="1"/>
       <c r="AK301" s="1"/>
       <c r="AL301" s="1"/>
-      <c r="AM301" s="1"/>
+      <c r="AM301" s="25"/>
       <c r="AN301" s="1"/>
       <c r="AO301" s="1"/>
       <c r="AP301" s="1"/>
@@ -23132,7 +23139,7 @@
       <c r="AJ302" s="1"/>
       <c r="AK302" s="1"/>
       <c r="AL302" s="1"/>
-      <c r="AM302" s="1"/>
+      <c r="AM302" s="25"/>
       <c r="AN302" s="1"/>
       <c r="AO302" s="1"/>
       <c r="AP302" s="1"/>
@@ -23187,7 +23194,7 @@
       <c r="AJ303" s="1"/>
       <c r="AK303" s="1"/>
       <c r="AL303" s="1"/>
-      <c r="AM303" s="1"/>
+      <c r="AM303" s="25"/>
       <c r="AN303" s="1"/>
       <c r="AO303" s="1"/>
       <c r="AP303" s="1"/>
@@ -23242,7 +23249,7 @@
       <c r="AJ304" s="1"/>
       <c r="AK304" s="1"/>
       <c r="AL304" s="1"/>
-      <c r="AM304" s="1"/>
+      <c r="AM304" s="25"/>
       <c r="AN304" s="1"/>
       <c r="AO304" s="1"/>
       <c r="AP304" s="1"/>
@@ -23297,7 +23304,7 @@
       <c r="AJ305" s="1"/>
       <c r="AK305" s="1"/>
       <c r="AL305" s="1"/>
-      <c r="AM305" s="1"/>
+      <c r="AM305" s="25"/>
       <c r="AN305" s="1"/>
       <c r="AO305" s="1"/>
       <c r="AP305" s="1"/>
@@ -23352,7 +23359,7 @@
       <c r="AJ306" s="1"/>
       <c r="AK306" s="1"/>
       <c r="AL306" s="1"/>
-      <c r="AM306" s="1"/>
+      <c r="AM306" s="25"/>
       <c r="AN306" s="1"/>
       <c r="AO306" s="1"/>
       <c r="AP306" s="1"/>
@@ -23407,7 +23414,7 @@
       <c r="AJ307" s="1"/>
       <c r="AK307" s="1"/>
       <c r="AL307" s="1"/>
-      <c r="AM307" s="1"/>
+      <c r="AM307" s="25"/>
       <c r="AN307" s="1"/>
       <c r="AO307" s="1"/>
       <c r="AP307" s="1"/>
@@ -23462,7 +23469,7 @@
       <c r="AJ308" s="1"/>
       <c r="AK308" s="1"/>
       <c r="AL308" s="1"/>
-      <c r="AM308" s="1"/>
+      <c r="AM308" s="25"/>
       <c r="AN308" s="1"/>
       <c r="AO308" s="1"/>
       <c r="AP308" s="1"/>
@@ -23517,7 +23524,7 @@
       <c r="AJ309" s="1"/>
       <c r="AK309" s="1"/>
       <c r="AL309" s="1"/>
-      <c r="AM309" s="1"/>
+      <c r="AM309" s="25"/>
       <c r="AN309" s="1"/>
       <c r="AO309" s="1"/>
       <c r="AP309" s="1"/>
@@ -23572,7 +23579,7 @@
       <c r="AJ310" s="1"/>
       <c r="AK310" s="1"/>
       <c r="AL310" s="1"/>
-      <c r="AM310" s="1"/>
+      <c r="AM310" s="25"/>
       <c r="AN310" s="1"/>
       <c r="AO310" s="1"/>
       <c r="AP310" s="1"/>
@@ -23627,7 +23634,7 @@
       <c r="AJ311" s="1"/>
       <c r="AK311" s="1"/>
       <c r="AL311" s="1"/>
-      <c r="AM311" s="1"/>
+      <c r="AM311" s="25"/>
       <c r="AN311" s="1"/>
       <c r="AO311" s="1"/>
       <c r="AP311" s="1"/>
@@ -23682,7 +23689,7 @@
       <c r="AJ312" s="1"/>
       <c r="AK312" s="1"/>
       <c r="AL312" s="1"/>
-      <c r="AM312" s="1"/>
+      <c r="AM312" s="25"/>
       <c r="AN312" s="1"/>
       <c r="AO312" s="1"/>
       <c r="AP312" s="1"/>
@@ -23737,7 +23744,7 @@
       <c r="AJ313" s="1"/>
       <c r="AK313" s="1"/>
       <c r="AL313" s="1"/>
-      <c r="AM313" s="1"/>
+      <c r="AM313" s="25"/>
       <c r="AN313" s="1"/>
       <c r="AO313" s="1"/>
       <c r="AP313" s="1"/>
@@ -23792,7 +23799,7 @@
       <c r="AJ314" s="1"/>
       <c r="AK314" s="1"/>
       <c r="AL314" s="1"/>
-      <c r="AM314" s="1"/>
+      <c r="AM314" s="25"/>
       <c r="AN314" s="1"/>
       <c r="AO314" s="1"/>
       <c r="AP314" s="1"/>
@@ -23847,7 +23854,7 @@
       <c r="AJ315" s="1"/>
       <c r="AK315" s="1"/>
       <c r="AL315" s="1"/>
-      <c r="AM315" s="1"/>
+      <c r="AM315" s="25"/>
       <c r="AN315" s="1"/>
       <c r="AO315" s="1"/>
       <c r="AP315" s="1"/>
@@ -23902,7 +23909,7 @@
       <c r="AJ316" s="1"/>
       <c r="AK316" s="1"/>
       <c r="AL316" s="1"/>
-      <c r="AM316" s="1"/>
+      <c r="AM316" s="25"/>
       <c r="AN316" s="1"/>
       <c r="AO316" s="1"/>
       <c r="AP316" s="1"/>
@@ -23957,7 +23964,7 @@
       <c r="AJ317" s="1"/>
       <c r="AK317" s="1"/>
       <c r="AL317" s="1"/>
-      <c r="AM317" s="1"/>
+      <c r="AM317" s="25"/>
       <c r="AN317" s="1"/>
       <c r="AO317" s="1"/>
       <c r="AP317" s="1"/>
@@ -24012,7 +24019,7 @@
       <c r="AJ318" s="1"/>
       <c r="AK318" s="1"/>
       <c r="AL318" s="1"/>
-      <c r="AM318" s="1"/>
+      <c r="AM318" s="25"/>
       <c r="AN318" s="1"/>
       <c r="AO318" s="1"/>
       <c r="AP318" s="1"/>
@@ -24067,7 +24074,7 @@
       <c r="AJ319" s="1"/>
       <c r="AK319" s="1"/>
       <c r="AL319" s="1"/>
-      <c r="AM319" s="1"/>
+      <c r="AM319" s="25"/>
       <c r="AN319" s="1"/>
       <c r="AO319" s="1"/>
       <c r="AP319" s="1"/>
@@ -24122,7 +24129,7 @@
       <c r="AJ320" s="1"/>
       <c r="AK320" s="1"/>
       <c r="AL320" s="1"/>
-      <c r="AM320" s="1"/>
+      <c r="AM320" s="25"/>
       <c r="AN320" s="1"/>
       <c r="AO320" s="1"/>
       <c r="AP320" s="1"/>
@@ -24177,7 +24184,7 @@
       <c r="AJ321" s="1"/>
       <c r="AK321" s="1"/>
       <c r="AL321" s="1"/>
-      <c r="AM321" s="1"/>
+      <c r="AM321" s="25"/>
       <c r="AN321" s="1"/>
       <c r="AO321" s="1"/>
       <c r="AP321" s="1"/>
@@ -24232,7 +24239,7 @@
       <c r="AJ322" s="1"/>
       <c r="AK322" s="1"/>
       <c r="AL322" s="1"/>
-      <c r="AM322" s="1"/>
+      <c r="AM322" s="25"/>
       <c r="AN322" s="1"/>
       <c r="AO322" s="1"/>
       <c r="AP322" s="1"/>
@@ -24287,7 +24294,7 @@
       <c r="AJ323" s="1"/>
       <c r="AK323" s="1"/>
       <c r="AL323" s="1"/>
-      <c r="AM323" s="1"/>
+      <c r="AM323" s="25"/>
       <c r="AN323" s="1"/>
       <c r="AO323" s="1"/>
       <c r="AP323" s="1"/>
@@ -24342,7 +24349,7 @@
       <c r="AJ324" s="1"/>
       <c r="AK324" s="1"/>
       <c r="AL324" s="1"/>
-      <c r="AM324" s="1"/>
+      <c r="AM324" s="25"/>
       <c r="AN324" s="1"/>
       <c r="AO324" s="1"/>
       <c r="AP324" s="1"/>
@@ -24397,7 +24404,7 @@
       <c r="AJ325" s="1"/>
       <c r="AK325" s="1"/>
       <c r="AL325" s="1"/>
-      <c r="AM325" s="1"/>
+      <c r="AM325" s="25"/>
       <c r="AN325" s="1"/>
       <c r="AO325" s="1"/>
       <c r="AP325" s="1"/>
@@ -24452,7 +24459,7 @@
       <c r="AJ326" s="1"/>
       <c r="AK326" s="1"/>
       <c r="AL326" s="1"/>
-      <c r="AM326" s="1"/>
+      <c r="AM326" s="25"/>
       <c r="AN326" s="1"/>
       <c r="AO326" s="1"/>
       <c r="AP326" s="1"/>
@@ -24507,7 +24514,7 @@
       <c r="AJ327" s="1"/>
       <c r="AK327" s="1"/>
       <c r="AL327" s="1"/>
-      <c r="AM327" s="1"/>
+      <c r="AM327" s="25"/>
       <c r="AN327" s="1"/>
       <c r="AO327" s="1"/>
       <c r="AP327" s="1"/>
@@ -24562,7 +24569,7 @@
       <c r="AJ328" s="1"/>
       <c r="AK328" s="1"/>
       <c r="AL328" s="1"/>
-      <c r="AM328" s="1"/>
+      <c r="AM328" s="25"/>
       <c r="AN328" s="1"/>
       <c r="AO328" s="1"/>
       <c r="AP328" s="1"/>
@@ -24617,7 +24624,7 @@
       <c r="AJ329" s="1"/>
       <c r="AK329" s="1"/>
       <c r="AL329" s="1"/>
-      <c r="AM329" s="1"/>
+      <c r="AM329" s="25"/>
       <c r="AN329" s="1"/>
       <c r="AO329" s="1"/>
       <c r="AP329" s="1"/>
@@ -24672,7 +24679,7 @@
       <c r="AJ330" s="1"/>
       <c r="AK330" s="1"/>
       <c r="AL330" s="1"/>
-      <c r="AM330" s="1"/>
+      <c r="AM330" s="25"/>
       <c r="AN330" s="1"/>
       <c r="AO330" s="1"/>
       <c r="AP330" s="1"/>
@@ -24727,7 +24734,7 @@
       <c r="AJ331" s="1"/>
       <c r="AK331" s="1"/>
       <c r="AL331" s="1"/>
-      <c r="AM331" s="1"/>
+      <c r="AM331" s="25"/>
       <c r="AN331" s="1"/>
       <c r="AO331" s="1"/>
       <c r="AP331" s="1"/>
@@ -24782,7 +24789,7 @@
       <c r="AJ332" s="1"/>
       <c r="AK332" s="1"/>
       <c r="AL332" s="1"/>
-      <c r="AM332" s="1"/>
+      <c r="AM332" s="25"/>
       <c r="AN332" s="1"/>
       <c r="AO332" s="1"/>
       <c r="AP332" s="1"/>
@@ -24837,7 +24844,7 @@
       <c r="AJ333" s="1"/>
       <c r="AK333" s="1"/>
       <c r="AL333" s="1"/>
-      <c r="AM333" s="1"/>
+      <c r="AM333" s="25"/>
       <c r="AN333" s="1"/>
       <c r="AO333" s="1"/>
       <c r="AP333" s="1"/>
@@ -24892,7 +24899,7 @@
       <c r="AJ334" s="1"/>
       <c r="AK334" s="1"/>
       <c r="AL334" s="1"/>
-      <c r="AM334" s="1"/>
+      <c r="AM334" s="25"/>
       <c r="AN334" s="1"/>
       <c r="AO334" s="1"/>
       <c r="AP334" s="1"/>
@@ -24947,7 +24954,7 @@
       <c r="AJ335" s="1"/>
       <c r="AK335" s="1"/>
       <c r="AL335" s="1"/>
-      <c r="AM335" s="1"/>
+      <c r="AM335" s="25"/>
       <c r="AN335" s="1"/>
       <c r="AO335" s="1"/>
       <c r="AP335" s="1"/>
@@ -25002,7 +25009,7 @@
       <c r="AJ336" s="1"/>
       <c r="AK336" s="1"/>
       <c r="AL336" s="1"/>
-      <c r="AM336" s="1"/>
+      <c r="AM336" s="25"/>
       <c r="AN336" s="1"/>
       <c r="AO336" s="1"/>
       <c r="AP336" s="1"/>
@@ -25057,7 +25064,7 @@
       <c r="AJ337" s="1"/>
       <c r="AK337" s="1"/>
       <c r="AL337" s="1"/>
-      <c r="AM337" s="1"/>
+      <c r="AM337" s="25"/>
       <c r="AN337" s="1"/>
       <c r="AO337" s="1"/>
       <c r="AP337" s="1"/>
@@ -25112,7 +25119,7 @@
       <c r="AJ338" s="1"/>
       <c r="AK338" s="1"/>
       <c r="AL338" s="1"/>
-      <c r="AM338" s="1"/>
+      <c r="AM338" s="25"/>
       <c r="AN338" s="1"/>
       <c r="AO338" s="1"/>
       <c r="AP338" s="1"/>
@@ -25167,7 +25174,7 @@
       <c r="AJ339" s="1"/>
       <c r="AK339" s="1"/>
       <c r="AL339" s="1"/>
-      <c r="AM339" s="1"/>
+      <c r="AM339" s="25"/>
       <c r="AN339" s="1"/>
       <c r="AO339" s="1"/>
       <c r="AP339" s="1"/>
@@ -25222,7 +25229,7 @@
       <c r="AJ340" s="1"/>
       <c r="AK340" s="1"/>
       <c r="AL340" s="1"/>
-      <c r="AM340" s="1"/>
+      <c r="AM340" s="25"/>
       <c r="AN340" s="1"/>
       <c r="AO340" s="1"/>
       <c r="AP340" s="1"/>
@@ -25277,7 +25284,7 @@
       <c r="AJ341" s="1"/>
       <c r="AK341" s="1"/>
       <c r="AL341" s="1"/>
-      <c r="AM341" s="1"/>
+      <c r="AM341" s="25"/>
       <c r="AN341" s="1"/>
       <c r="AO341" s="1"/>
       <c r="AP341" s="1"/>
@@ -25332,7 +25339,7 @@
       <c r="AJ342" s="1"/>
       <c r="AK342" s="1"/>
       <c r="AL342" s="1"/>
-      <c r="AM342" s="1"/>
+      <c r="AM342" s="25"/>
       <c r="AN342" s="1"/>
       <c r="AO342" s="1"/>
       <c r="AP342" s="1"/>
@@ -25387,7 +25394,7 @@
       <c r="AJ343" s="1"/>
       <c r="AK343" s="1"/>
       <c r="AL343" s="1"/>
-      <c r="AM343" s="1"/>
+      <c r="AM343" s="25"/>
       <c r="AN343" s="1"/>
       <c r="AO343" s="1"/>
       <c r="AP343" s="1"/>
@@ -25442,7 +25449,7 @@
       <c r="AJ344" s="1"/>
       <c r="AK344" s="1"/>
       <c r="AL344" s="1"/>
-      <c r="AM344" s="1"/>
+      <c r="AM344" s="25"/>
       <c r="AN344" s="1"/>
       <c r="AO344" s="1"/>
       <c r="AP344" s="1"/>
@@ -25497,7 +25504,7 @@
       <c r="AJ345" s="1"/>
       <c r="AK345" s="1"/>
       <c r="AL345" s="1"/>
-      <c r="AM345" s="1"/>
+      <c r="AM345" s="25"/>
       <c r="AN345" s="1"/>
       <c r="AO345" s="1"/>
       <c r="AP345" s="1"/>
@@ -25552,7 +25559,7 @@
       <c r="AJ346" s="1"/>
       <c r="AK346" s="1"/>
       <c r="AL346" s="1"/>
-      <c r="AM346" s="1"/>
+      <c r="AM346" s="25"/>
       <c r="AN346" s="1"/>
       <c r="AO346" s="1"/>
       <c r="AP346" s="1"/>
@@ -25607,7 +25614,7 @@
       <c r="AJ347" s="1"/>
       <c r="AK347" s="1"/>
       <c r="AL347" s="1"/>
-      <c r="AM347" s="1"/>
+      <c r="AM347" s="25"/>
       <c r="AN347" s="1"/>
       <c r="AO347" s="1"/>
       <c r="AP347" s="1"/>
@@ -25662,7 +25669,7 @@
       <c r="AJ348" s="1"/>
       <c r="AK348" s="1"/>
       <c r="AL348" s="1"/>
-      <c r="AM348" s="1"/>
+      <c r="AM348" s="25"/>
       <c r="AN348" s="1"/>
       <c r="AO348" s="1"/>
       <c r="AP348" s="1"/>
@@ -25717,7 +25724,7 @@
       <c r="AJ349" s="1"/>
       <c r="AK349" s="1"/>
       <c r="AL349" s="1"/>
-      <c r="AM349" s="1"/>
+      <c r="AM349" s="25"/>
       <c r="AN349" s="1"/>
       <c r="AO349" s="1"/>
       <c r="AP349" s="1"/>
@@ -25772,7 +25779,7 @@
       <c r="AJ350" s="1"/>
       <c r="AK350" s="1"/>
       <c r="AL350" s="1"/>
-      <c r="AM350" s="1"/>
+      <c r="AM350" s="25"/>
       <c r="AN350" s="1"/>
       <c r="AO350" s="1"/>
       <c r="AP350" s="1"/>
@@ -25827,7 +25834,7 @@
       <c r="AJ351" s="1"/>
       <c r="AK351" s="1"/>
       <c r="AL351" s="1"/>
-      <c r="AM351" s="1"/>
+      <c r="AM351" s="25"/>
       <c r="AN351" s="1"/>
       <c r="AO351" s="1"/>
       <c r="AP351" s="1"/>
@@ -25882,7 +25889,7 @@
       <c r="AJ352" s="1"/>
       <c r="AK352" s="1"/>
       <c r="AL352" s="1"/>
-      <c r="AM352" s="1"/>
+      <c r="AM352" s="25"/>
       <c r="AN352" s="1"/>
       <c r="AO352" s="1"/>
       <c r="AP352" s="1"/>
@@ -25937,7 +25944,7 @@
       <c r="AJ353" s="1"/>
       <c r="AK353" s="1"/>
       <c r="AL353" s="1"/>
-      <c r="AM353" s="1"/>
+      <c r="AM353" s="25"/>
       <c r="AN353" s="1"/>
       <c r="AO353" s="1"/>
       <c r="AP353" s="1"/>
@@ -25992,7 +25999,7 @@
       <c r="AJ354" s="1"/>
       <c r="AK354" s="1"/>
       <c r="AL354" s="1"/>
-      <c r="AM354" s="1"/>
+      <c r="AM354" s="25"/>
       <c r="AN354" s="1"/>
       <c r="AO354" s="1"/>
       <c r="AP354" s="1"/>
@@ -26047,7 +26054,7 @@
       <c r="AJ355" s="1"/>
       <c r="AK355" s="1"/>
       <c r="AL355" s="1"/>
-      <c r="AM355" s="1"/>
+      <c r="AM355" s="25"/>
       <c r="AN355" s="1"/>
       <c r="AO355" s="1"/>
       <c r="AP355" s="1"/>
@@ -26102,7 +26109,7 @@
       <c r="AJ356" s="1"/>
       <c r="AK356" s="1"/>
       <c r="AL356" s="1"/>
-      <c r="AM356" s="1"/>
+      <c r="AM356" s="25"/>
       <c r="AN356" s="1"/>
       <c r="AO356" s="1"/>
       <c r="AP356" s="1"/>
@@ -26157,7 +26164,7 @@
       <c r="AJ357" s="1"/>
       <c r="AK357" s="1"/>
       <c r="AL357" s="1"/>
-      <c r="AM357" s="1"/>
+      <c r="AM357" s="25"/>
       <c r="AN357" s="1"/>
       <c r="AO357" s="1"/>
       <c r="AP357" s="1"/>
@@ -26212,7 +26219,7 @@
       <c r="AJ358" s="1"/>
       <c r="AK358" s="1"/>
       <c r="AL358" s="1"/>
-      <c r="AM358" s="1"/>
+      <c r="AM358" s="25"/>
       <c r="AN358" s="1"/>
       <c r="AO358" s="1"/>
       <c r="AP358" s="1"/>
@@ -26267,7 +26274,7 @@
       <c r="AJ359" s="1"/>
       <c r="AK359" s="1"/>
       <c r="AL359" s="1"/>
-      <c r="AM359" s="1"/>
+      <c r="AM359" s="25"/>
       <c r="AN359" s="1"/>
       <c r="AO359" s="1"/>
       <c r="AP359" s="1"/>
@@ -26322,7 +26329,7 @@
       <c r="AJ360" s="1"/>
       <c r="AK360" s="1"/>
       <c r="AL360" s="1"/>
-      <c r="AM360" s="1"/>
+      <c r="AM360" s="25"/>
       <c r="AN360" s="1"/>
       <c r="AO360" s="1"/>
       <c r="AP360" s="1"/>
@@ -26377,7 +26384,7 @@
       <c r="AJ361" s="1"/>
       <c r="AK361" s="1"/>
       <c r="AL361" s="1"/>
-      <c r="AM361" s="1"/>
+      <c r="AM361" s="25"/>
       <c r="AN361" s="1"/>
       <c r="AO361" s="1"/>
       <c r="AP361" s="1"/>
@@ -26432,7 +26439,7 @@
       <c r="AJ362" s="1"/>
       <c r="AK362" s="1"/>
       <c r="AL362" s="1"/>
-      <c r="AM362" s="1"/>
+      <c r="AM362" s="25"/>
       <c r="AN362" s="1"/>
       <c r="AO362" s="1"/>
       <c r="AP362" s="1"/>
@@ -26487,7 +26494,7 @@
       <c r="AJ363" s="1"/>
       <c r="AK363" s="1"/>
       <c r="AL363" s="1"/>
-      <c r="AM363" s="1"/>
+      <c r="AM363" s="25"/>
       <c r="AN363" s="1"/>
       <c r="AO363" s="1"/>
       <c r="AP363" s="1"/>
@@ -26542,7 +26549,7 @@
       <c r="AJ364" s="1"/>
       <c r="AK364" s="1"/>
       <c r="AL364" s="1"/>
-      <c r="AM364" s="1"/>
+      <c r="AM364" s="25"/>
       <c r="AN364" s="1"/>
       <c r="AO364" s="1"/>
       <c r="AP364" s="1"/>
@@ -26597,7 +26604,7 @@
       <c r="AJ365" s="1"/>
       <c r="AK365" s="1"/>
       <c r="AL365" s="1"/>
-      <c r="AM365" s="1"/>
+      <c r="AM365" s="25"/>
       <c r="AN365" s="1"/>
       <c r="AO365" s="1"/>
       <c r="AP365" s="1"/>
@@ -26652,7 +26659,7 @@
       <c r="AJ366" s="1"/>
       <c r="AK366" s="1"/>
       <c r="AL366" s="1"/>
-      <c r="AM366" s="1"/>
+      <c r="AM366" s="25"/>
       <c r="AN366" s="1"/>
       <c r="AO366" s="1"/>
       <c r="AP366" s="1"/>
@@ -26707,7 +26714,7 @@
       <c r="AJ367" s="1"/>
       <c r="AK367" s="1"/>
       <c r="AL367" s="1"/>
-      <c r="AM367" s="1"/>
+      <c r="AM367" s="25"/>
       <c r="AN367" s="1"/>
       <c r="AO367" s="1"/>
       <c r="AP367" s="1"/>
@@ -26762,7 +26769,7 @@
       <c r="AJ368" s="1"/>
       <c r="AK368" s="1"/>
       <c r="AL368" s="1"/>
-      <c r="AM368" s="1"/>
+      <c r="AM368" s="25"/>
       <c r="AN368" s="1"/>
       <c r="AO368" s="1"/>
       <c r="AP368" s="1"/>
@@ -26817,7 +26824,7 @@
       <c r="AJ369" s="1"/>
       <c r="AK369" s="1"/>
       <c r="AL369" s="1"/>
-      <c r="AM369" s="1"/>
+      <c r="AM369" s="25"/>
       <c r="AN369" s="1"/>
       <c r="AO369" s="1"/>
       <c r="AP369" s="1"/>
@@ -26872,7 +26879,7 @@
       <c r="AJ370" s="1"/>
       <c r="AK370" s="1"/>
       <c r="AL370" s="1"/>
-      <c r="AM370" s="1"/>
+      <c r="AM370" s="25"/>
       <c r="AN370" s="1"/>
       <c r="AO370" s="1"/>
       <c r="AP370" s="1"/>
@@ -26927,7 +26934,7 @@
       <c r="AJ371" s="1"/>
       <c r="AK371" s="1"/>
       <c r="AL371" s="1"/>
-      <c r="AM371" s="1"/>
+      <c r="AM371" s="25"/>
       <c r="AN371" s="1"/>
       <c r="AO371" s="1"/>
       <c r="AP371" s="1"/>
@@ -26982,7 +26989,7 @@
       <c r="AJ372" s="1"/>
       <c r="AK372" s="1"/>
       <c r="AL372" s="1"/>
-      <c r="AM372" s="1"/>
+      <c r="AM372" s="25"/>
       <c r="AN372" s="1"/>
       <c r="AO372" s="1"/>
       <c r="AP372" s="1"/>
@@ -27037,7 +27044,7 @@
       <c r="AJ373" s="1"/>
       <c r="AK373" s="1"/>
       <c r="AL373" s="1"/>
-      <c r="AM373" s="1"/>
+      <c r="AM373" s="25"/>
       <c r="AN373" s="1"/>
       <c r="AO373" s="1"/>
       <c r="AP373" s="1"/>
@@ -27092,7 +27099,7 @@
       <c r="AJ374" s="1"/>
       <c r="AK374" s="1"/>
       <c r="AL374" s="1"/>
-      <c r="AM374" s="1"/>
+      <c r="AM374" s="25"/>
       <c r="AN374" s="1"/>
       <c r="AO374" s="1"/>
       <c r="AP374" s="1"/>
@@ -27147,7 +27154,7 @@
       <c r="AJ375" s="1"/>
       <c r="AK375" s="1"/>
       <c r="AL375" s="1"/>
-      <c r="AM375" s="1"/>
+      <c r="AM375" s="25"/>
       <c r="AN375" s="1"/>
       <c r="AO375" s="1"/>
       <c r="AP375" s="1"/>
@@ -27202,7 +27209,7 @@
       <c r="AJ376" s="1"/>
       <c r="AK376" s="1"/>
       <c r="AL376" s="1"/>
-      <c r="AM376" s="1"/>
+      <c r="AM376" s="25"/>
       <c r="AN376" s="1"/>
       <c r="AO376" s="1"/>
       <c r="AP376" s="1"/>
@@ -27257,7 +27264,7 @@
       <c r="AJ377" s="1"/>
       <c r="AK377" s="1"/>
       <c r="AL377" s="1"/>
-      <c r="AM377" s="1"/>
+      <c r="AM377" s="25"/>
       <c r="AN377" s="1"/>
       <c r="AO377" s="1"/>
       <c r="AP377" s="1"/>
@@ -27312,7 +27319,7 @@
       <c r="AJ378" s="1"/>
       <c r="AK378" s="1"/>
       <c r="AL378" s="1"/>
-      <c r="AM378" s="1"/>
+      <c r="AM378" s="25"/>
       <c r="AN378" s="1"/>
       <c r="AO378" s="1"/>
       <c r="AP378" s="1"/>
@@ -27367,7 +27374,7 @@
       <c r="AJ379" s="1"/>
       <c r="AK379" s="1"/>
       <c r="AL379" s="1"/>
-      <c r="AM379" s="1"/>
+      <c r="AM379" s="25"/>
       <c r="AN379" s="1"/>
       <c r="AO379" s="1"/>
       <c r="AP379" s="1"/>
@@ -27422,7 +27429,7 @@
       <c r="AJ380" s="1"/>
       <c r="AK380" s="1"/>
       <c r="AL380" s="1"/>
-      <c r="AM380" s="1"/>
+      <c r="AM380" s="25"/>
       <c r="AN380" s="1"/>
       <c r="AO380" s="1"/>
       <c r="AP380" s="1"/>
@@ -27477,7 +27484,7 @@
       <c r="AJ381" s="1"/>
       <c r="AK381" s="1"/>
       <c r="AL381" s="1"/>
-      <c r="AM381" s="1"/>
+      <c r="AM381" s="25"/>
       <c r="AN381" s="1"/>
       <c r="AO381" s="1"/>
       <c r="AP381" s="1"/>
@@ -27532,7 +27539,7 @@
       <c r="AJ382" s="1"/>
       <c r="AK382" s="1"/>
       <c r="AL382" s="1"/>
-      <c r="AM382" s="1"/>
+      <c r="AM382" s="25"/>
       <c r="AN382" s="1"/>
       <c r="AO382" s="1"/>
       <c r="AP382" s="1"/>
@@ -27587,7 +27594,7 @@
       <c r="AJ383" s="1"/>
       <c r="AK383" s="1"/>
       <c r="AL383" s="1"/>
-      <c r="AM383" s="1"/>
+      <c r="AM383" s="25"/>
       <c r="AN383" s="1"/>
       <c r="AO383" s="1"/>
       <c r="AP383" s="1"/>
@@ -27642,7 +27649,7 @@
       <c r="AJ384" s="1"/>
       <c r="AK384" s="1"/>
       <c r="AL384" s="1"/>
-      <c r="AM384" s="1"/>
+      <c r="AM384" s="25"/>
       <c r="AN384" s="1"/>
       <c r="AO384" s="1"/>
       <c r="AP384" s="1"/>
@@ -27697,7 +27704,7 @@
       <c r="AJ385" s="1"/>
       <c r="AK385" s="1"/>
       <c r="AL385" s="1"/>
-      <c r="AM385" s="1"/>
+      <c r="AM385" s="25"/>
       <c r="AN385" s="1"/>
       <c r="AO385" s="1"/>
       <c r="AP385" s="1"/>
@@ -27752,7 +27759,7 @@
       <c r="AJ386" s="1"/>
       <c r="AK386" s="1"/>
       <c r="AL386" s="1"/>
-      <c r="AM386" s="1"/>
+      <c r="AM386" s="25"/>
       <c r="AN386" s="1"/>
       <c r="AO386" s="1"/>
       <c r="AP386" s="1"/>
@@ -27807,7 +27814,7 @@
       <c r="AJ387" s="1"/>
       <c r="AK387" s="1"/>
       <c r="AL387" s="1"/>
-      <c r="AM387" s="1"/>
+      <c r="AM387" s="25"/>
       <c r="AN387" s="1"/>
       <c r="AO387" s="1"/>
       <c r="AP387" s="1"/>
@@ -27862,7 +27869,7 @@
       <c r="AJ388" s="1"/>
       <c r="AK388" s="1"/>
       <c r="AL388" s="1"/>
-      <c r="AM388" s="1"/>
+      <c r="AM388" s="25"/>
       <c r="AN388" s="1"/>
       <c r="AO388" s="1"/>
       <c r="AP388" s="1"/>
@@ -27917,7 +27924,7 @@
       <c r="AJ389" s="1"/>
       <c r="AK389" s="1"/>
       <c r="AL389" s="1"/>
-      <c r="AM389" s="1"/>
+      <c r="AM389" s="25"/>
       <c r="AN389" s="1"/>
       <c r="AO389" s="1"/>
       <c r="AP389" s="1"/>
@@ -27972,7 +27979,7 @@
       <c r="AJ390" s="1"/>
       <c r="AK390" s="1"/>
       <c r="AL390" s="1"/>
-      <c r="AM390" s="1"/>
+      <c r="AM390" s="25"/>
       <c r="AN390" s="1"/>
       <c r="AO390" s="1"/>
       <c r="AP390" s="1"/>
@@ -28027,7 +28034,7 @@
       <c r="AJ391" s="1"/>
       <c r="AK391" s="1"/>
       <c r="AL391" s="1"/>
-      <c r="AM391" s="1"/>
+      <c r="AM391" s="25"/>
       <c r="AN391" s="1"/>
       <c r="AO391" s="1"/>
       <c r="AP391" s="1"/>
@@ -28082,7 +28089,7 @@
       <c r="AJ392" s="1"/>
       <c r="AK392" s="1"/>
       <c r="AL392" s="1"/>
-      <c r="AM392" s="1"/>
+      <c r="AM392" s="25"/>
       <c r="AN392" s="1"/>
       <c r="AO392" s="1"/>
       <c r="AP392" s="1"/>
@@ -28137,7 +28144,7 @@
       <c r="AJ393" s="1"/>
       <c r="AK393" s="1"/>
       <c r="AL393" s="1"/>
-      <c r="AM393" s="1"/>
+      <c r="AM393" s="25"/>
       <c r="AN393" s="1"/>
       <c r="AO393" s="1"/>
       <c r="AP393" s="1"/>
@@ -28192,7 +28199,7 @@
       <c r="AJ394" s="1"/>
       <c r="AK394" s="1"/>
       <c r="AL394" s="1"/>
-      <c r="AM394" s="1"/>
+      <c r="AM394" s="25"/>
       <c r="AN394" s="1"/>
       <c r="AO394" s="1"/>
       <c r="AP394" s="1"/>
@@ -28247,7 +28254,7 @@
       <c r="AJ395" s="1"/>
       <c r="AK395" s="1"/>
       <c r="AL395" s="1"/>
-      <c r="AM395" s="1"/>
+      <c r="AM395" s="25"/>
       <c r="AN395" s="1"/>
       <c r="AO395" s="1"/>
       <c r="AP395" s="1"/>
@@ -28302,7 +28309,7 @@
       <c r="AJ396" s="1"/>
       <c r="AK396" s="1"/>
       <c r="AL396" s="1"/>
-      <c r="AM396" s="1"/>
+      <c r="AM396" s="25"/>
       <c r="AN396" s="1"/>
       <c r="AO396" s="1"/>
       <c r="AP396" s="1"/>
@@ -28357,7 +28364,7 @@
       <c r="AJ397" s="1"/>
       <c r="AK397" s="1"/>
       <c r="AL397" s="1"/>
-      <c r="AM397" s="1"/>
+      <c r="AM397" s="25"/>
       <c r="AN397" s="1"/>
       <c r="AO397" s="1"/>
       <c r="AP397" s="1"/>
@@ -28412,7 +28419,7 @@
       <c r="AJ398" s="1"/>
       <c r="AK398" s="1"/>
       <c r="AL398" s="1"/>
-      <c r="AM398" s="1"/>
+      <c r="AM398" s="25"/>
       <c r="AN398" s="1"/>
       <c r="AO398" s="1"/>
       <c r="AP398" s="1"/>
@@ -28467,7 +28474,7 @@
       <c r="AJ399" s="1"/>
       <c r="AK399" s="1"/>
       <c r="AL399" s="1"/>
-      <c r="AM399" s="1"/>
+      <c r="AM399" s="25"/>
       <c r="AN399" s="1"/>
       <c r="AO399" s="1"/>
       <c r="AP399" s="1"/>
@@ -28522,7 +28529,7 @@
       <c r="AJ400" s="1"/>
       <c r="AK400" s="1"/>
       <c r="AL400" s="1"/>
-      <c r="AM400" s="1"/>
+      <c r="AM400" s="25"/>
       <c r="AN400" s="1"/>
       <c r="AO400" s="1"/>
       <c r="AP400" s="1"/>
@@ -28577,7 +28584,7 @@
       <c r="AJ401" s="1"/>
       <c r="AK401" s="1"/>
       <c r="AL401" s="1"/>
-      <c r="AM401" s="1"/>
+      <c r="AM401" s="25"/>
       <c r="AN401" s="1"/>
       <c r="AO401" s="1"/>
       <c r="AP401" s="1"/>
@@ -28632,7 +28639,7 @@
       <c r="AJ402" s="1"/>
       <c r="AK402" s="1"/>
       <c r="AL402" s="1"/>
-      <c r="AM402" s="1"/>
+      <c r="AM402" s="25"/>
       <c r="AN402" s="1"/>
       <c r="AO402" s="1"/>
       <c r="AP402" s="1"/>
@@ -28687,7 +28694,7 @@
       <c r="AJ403" s="1"/>
       <c r="AK403" s="1"/>
       <c r="AL403" s="1"/>
-      <c r="AM403" s="1"/>
+      <c r="AM403" s="25"/>
       <c r="AN403" s="1"/>
       <c r="AO403" s="1"/>
       <c r="AP403" s="1"/>
@@ -28742,7 +28749,7 @@
       <c r="AJ404" s="1"/>
       <c r="AK404" s="1"/>
       <c r="AL404" s="1"/>
-      <c r="AM404" s="1"/>
+      <c r="AM404" s="25"/>
       <c r="AN404" s="1"/>
       <c r="AO404" s="1"/>
       <c r="AP404" s="1"/>
@@ -28797,7 +28804,7 @@
       <c r="AJ405" s="1"/>
       <c r="AK405" s="1"/>
       <c r="AL405" s="1"/>
-      <c r="AM405" s="1"/>
+      <c r="AM405" s="25"/>
       <c r="AN405" s="1"/>
       <c r="AO405" s="1"/>
       <c r="AP405" s="1"/>
@@ -28852,7 +28859,7 @@
       <c r="AJ406" s="1"/>
       <c r="AK406" s="1"/>
       <c r="AL406" s="1"/>
-      <c r="AM406" s="1"/>
+      <c r="AM406" s="25"/>
       <c r="AN406" s="1"/>
       <c r="AO406" s="1"/>
       <c r="AP406" s="1"/>
@@ -28907,7 +28914,7 @@
       <c r="AJ407" s="1"/>
       <c r="AK407" s="1"/>
       <c r="AL407" s="1"/>
-      <c r="AM407" s="1"/>
+      <c r="AM407" s="25"/>
       <c r="AN407" s="1"/>
       <c r="AO407" s="1"/>
       <c r="AP407" s="1"/>
@@ -28962,7 +28969,7 @@
       <c r="AJ408" s="1"/>
       <c r="AK408" s="1"/>
       <c r="AL408" s="1"/>
-      <c r="AM408" s="1"/>
+      <c r="AM408" s="25"/>
       <c r="AN408" s="1"/>
       <c r="AO408" s="1"/>
       <c r="AP408" s="1"/>
@@ -29017,7 +29024,7 @@
       <c r="AJ409" s="1"/>
       <c r="AK409" s="1"/>
       <c r="AL409" s="1"/>
-      <c r="AM409" s="1"/>
+      <c r="AM409" s="25"/>
       <c r="AN409" s="1"/>
       <c r="AO409" s="1"/>
       <c r="AP409" s="1"/>
@@ -29072,7 +29079,7 @@
       <c r="AJ410" s="1"/>
       <c r="AK410" s="1"/>
       <c r="AL410" s="1"/>
-      <c r="AM410" s="1"/>
+      <c r="AM410" s="25"/>
       <c r="AN410" s="1"/>
       <c r="AO410" s="1"/>
       <c r="AP410" s="1"/>
@@ -29127,7 +29134,7 @@
       <c r="AJ411" s="1"/>
       <c r="AK411" s="1"/>
       <c r="AL411" s="1"/>
-      <c r="AM411" s="1"/>
+      <c r="AM411" s="25"/>
       <c r="AN411" s="1"/>
       <c r="AO411" s="1"/>
       <c r="AP411" s="1"/>
@@ -29182,7 +29189,7 @@
       <c r="AJ412" s="1"/>
       <c r="AK412" s="1"/>
       <c r="AL412" s="1"/>
-      <c r="AM412" s="1"/>
+      <c r="AM412" s="25"/>
       <c r="AN412" s="1"/>
       <c r="AO412" s="1"/>
       <c r="AP412" s="1"/>
@@ -29237,7 +29244,7 @@
       <c r="AJ413" s="1"/>
       <c r="AK413" s="1"/>
       <c r="AL413" s="1"/>
-      <c r="AM413" s="1"/>
+      <c r="AM413" s="25"/>
       <c r="AN413" s="1"/>
       <c r="AO413" s="1"/>
       <c r="AP413" s="1"/>
@@ -29292,7 +29299,7 @@
       <c r="AJ414" s="1"/>
       <c r="AK414" s="1"/>
       <c r="AL414" s="1"/>
-      <c r="AM414" s="1"/>
+      <c r="AM414" s="25"/>
       <c r="AN414" s="1"/>
       <c r="AO414" s="1"/>
       <c r="AP414" s="1"/>
@@ -29347,7 +29354,7 @@
       <c r="AJ415" s="1"/>
       <c r="AK415" s="1"/>
       <c r="AL415" s="1"/>
-      <c r="AM415" s="1"/>
+      <c r="AM415" s="25"/>
       <c r="AN415" s="1"/>
       <c r="AO415" s="1"/>
       <c r="AP415" s="1"/>
@@ -29402,7 +29409,7 @@
       <c r="AJ416" s="1"/>
       <c r="AK416" s="1"/>
       <c r="AL416" s="1"/>
-      <c r="AM416" s="1"/>
+      <c r="AM416" s="25"/>
       <c r="AN416" s="1"/>
       <c r="AO416" s="1"/>
       <c r="AP416" s="1"/>
@@ -29457,7 +29464,7 @@
       <c r="AJ417" s="1"/>
       <c r="AK417" s="1"/>
       <c r="AL417" s="1"/>
-      <c r="AM417" s="1"/>
+      <c r="AM417" s="25"/>
       <c r="AN417" s="1"/>
       <c r="AO417" s="1"/>
       <c r="AP417" s="1"/>
@@ -29512,7 +29519,7 @@
       <c r="AJ418" s="1"/>
       <c r="AK418" s="1"/>
       <c r="AL418" s="1"/>
-      <c r="AM418" s="1"/>
+      <c r="AM418" s="25"/>
       <c r="AN418" s="1"/>
       <c r="AO418" s="1"/>
       <c r="AP418" s="1"/>
@@ -29567,7 +29574,7 @@
       <c r="AJ419" s="1"/>
       <c r="AK419" s="1"/>
       <c r="AL419" s="1"/>
-      <c r="AM419" s="1"/>
+      <c r="AM419" s="25"/>
       <c r="AN419" s="1"/>
       <c r="AO419" s="1"/>
       <c r="AP419" s="1"/>
@@ -29622,7 +29629,7 @@
       <c r="AJ420" s="1"/>
       <c r="AK420" s="1"/>
       <c r="AL420" s="1"/>
-      <c r="AM420" s="1"/>
+      <c r="AM420" s="25"/>
       <c r="AN420" s="1"/>
       <c r="AO420" s="1"/>
       <c r="AP420" s="1"/>
@@ -29677,7 +29684,7 @@
       <c r="AJ421" s="1"/>
       <c r="AK421" s="1"/>
       <c r="AL421" s="1"/>
-      <c r="AM421" s="1"/>
+      <c r="AM421" s="25"/>
       <c r="AN421" s="1"/>
       <c r="AO421" s="1"/>
       <c r="AP421" s="1"/>
@@ -29732,7 +29739,7 @@
       <c r="AJ422" s="1"/>
       <c r="AK422" s="1"/>
       <c r="AL422" s="1"/>
-      <c r="AM422" s="1"/>
+      <c r="AM422" s="25"/>
       <c r="AN422" s="1"/>
       <c r="AO422" s="1"/>
       <c r="AP422" s="1"/>
@@ -29787,7 +29794,7 @@
       <c r="AJ423" s="1"/>
       <c r="AK423" s="1"/>
       <c r="AL423" s="1"/>
-      <c r="AM423" s="1"/>
+      <c r="AM423" s="25"/>
       <c r="AN423" s="1"/>
       <c r="AO423" s="1"/>
       <c r="AP423" s="1"/>
@@ -29842,7 +29849,7 @@
       <c r="AJ424" s="1"/>
       <c r="AK424" s="1"/>
       <c r="AL424" s="1"/>
-      <c r="AM424" s="1"/>
+      <c r="AM424" s="25"/>
       <c r="AN424" s="1"/>
       <c r="AO424" s="1"/>
       <c r="AP424" s="1"/>
@@ -29897,7 +29904,7 @@
       <c r="AJ425" s="1"/>
       <c r="AK425" s="1"/>
       <c r="AL425" s="1"/>
-      <c r="AM425" s="1"/>
+      <c r="AM425" s="25"/>
       <c r="AN425" s="1"/>
       <c r="AO425" s="1"/>
       <c r="AP425" s="1"/>
@@ -29952,7 +29959,7 @@
       <c r="AJ426" s="1"/>
       <c r="AK426" s="1"/>
       <c r="AL426" s="1"/>
-      <c r="AM426" s="1"/>
+      <c r="AM426" s="25"/>
       <c r="AN426" s="1"/>
       <c r="AO426" s="1"/>
       <c r="AP426" s="1"/>
@@ -30007,7 +30014,7 @@
       <c r="AJ427" s="1"/>
       <c r="AK427" s="1"/>
       <c r="AL427" s="1"/>
-      <c r="AM427" s="1"/>
+      <c r="AM427" s="25"/>
       <c r="AN427" s="1"/>
       <c r="AO427" s="1"/>
       <c r="AP427" s="1"/>
@@ -30062,7 +30069,7 @@
       <c r="AJ428" s="1"/>
       <c r="AK428" s="1"/>
       <c r="AL428" s="1"/>
-      <c r="AM428" s="1"/>
+      <c r="AM428" s="25"/>
       <c r="AN428" s="1"/>
       <c r="AO428" s="1"/>
       <c r="AP428" s="1"/>
@@ -30117,7 +30124,7 @@
       <c r="AJ429" s="1"/>
       <c r="AK429" s="1"/>
       <c r="AL429" s="1"/>
-      <c r="AM429" s="1"/>
+      <c r="AM429" s="25"/>
       <c r="AN429" s="1"/>
       <c r="AO429" s="1"/>
       <c r="AP429" s="1"/>
@@ -30172,7 +30179,7 @@
       <c r="AJ430" s="1"/>
       <c r="AK430" s="1"/>
       <c r="AL430" s="1"/>
-      <c r="AM430" s="1"/>
+      <c r="AM430" s="25"/>
       <c r="AN430" s="1"/>
       <c r="AO430" s="1"/>
       <c r="AP430" s="1"/>
@@ -30227,7 +30234,7 @@
       <c r="AJ431" s="1"/>
       <c r="AK431" s="1"/>
       <c r="AL431" s="1"/>
-      <c r="AM431" s="1"/>
+      <c r="AM431" s="25"/>
       <c r="AN431" s="1"/>
       <c r="AO431" s="1"/>
       <c r="AP431" s="1"/>
@@ -30282,7 +30289,7 @@
       <c r="AJ432" s="1"/>
       <c r="AK432" s="1"/>
       <c r="AL432" s="1"/>
-      <c r="AM432" s="1"/>
+      <c r="AM432" s="25"/>
       <c r="AN432" s="1"/>
       <c r="AO432" s="1"/>
       <c r="AP432" s="1"/>
@@ -30337,7 +30344,7 @@
       <c r="AJ433" s="1"/>
       <c r="AK433" s="1"/>
       <c r="AL433" s="1"/>
-      <c r="AM433" s="1"/>
+      <c r="AM433" s="25"/>
       <c r="AN433" s="1"/>
       <c r="AO433" s="1"/>
       <c r="AP433" s="1"/>
@@ -30392,7 +30399,7 @@
       <c r="AJ434" s="1"/>
       <c r="AK434" s="1"/>
       <c r="AL434" s="1"/>
-      <c r="AM434" s="1"/>
+      <c r="AM434" s="25"/>
       <c r="AN434" s="1"/>
       <c r="AO434" s="1"/>
       <c r="AP434" s="1"/>
@@ -30447,7 +30454,7 @@
       <c r="AJ435" s="1"/>
       <c r="AK435" s="1"/>
       <c r="AL435" s="1"/>
-      <c r="AM435" s="1"/>
+      <c r="AM435" s="25"/>
       <c r="AN435" s="1"/>
       <c r="AO435" s="1"/>
       <c r="AP435" s="1"/>
@@ -30502,7 +30509,7 @@
       <c r="AJ436" s="1"/>
       <c r="AK436" s="1"/>
       <c r="AL436" s="1"/>
-      <c r="AM436" s="1"/>
+      <c r="AM436" s="25"/>
       <c r="AN436" s="1"/>
       <c r="AO436" s="1"/>
       <c r="AP436" s="1"/>
@@ -30557,7 +30564,7 @@
       <c r="AJ437" s="1"/>
       <c r="AK437" s="1"/>
       <c r="AL437" s="1"/>
-      <c r="AM437" s="1"/>
+      <c r="AM437" s="25"/>
       <c r="AN437" s="1"/>
       <c r="AO437" s="1"/>
       <c r="AP437" s="1"/>
@@ -30612,7 +30619,7 @@
       <c r="AJ438" s="1"/>
       <c r="AK438" s="1"/>
       <c r="AL438" s="1"/>
-      <c r="AM438" s="1"/>
+      <c r="AM438" s="25"/>
       <c r="AN438" s="1"/>
       <c r="AO438" s="1"/>
       <c r="AP438" s="1"/>
@@ -30667,7 +30674,7 @@
       <c r="AJ439" s="1"/>
       <c r="AK439" s="1"/>
       <c r="AL439" s="1"/>
-      <c r="AM439" s="1"/>
+      <c r="AM439" s="25"/>
       <c r="AN439" s="1"/>
       <c r="AO439" s="1"/>
       <c r="AP439" s="1"/>
@@ -30722,7 +30729,7 @@
       <c r="AJ440" s="1"/>
       <c r="AK440" s="1"/>
       <c r="AL440" s="1"/>
-      <c r="AM440" s="1"/>
+      <c r="AM440" s="25"/>
       <c r="AN440" s="1"/>
       <c r="AO440" s="1"/>
       <c r="AP440" s="1"/>
@@ -30777,7 +30784,7 @@
       <c r="AJ441" s="1"/>
       <c r="AK441" s="1"/>
       <c r="AL441" s="1"/>
-      <c r="AM441" s="1"/>
+      <c r="AM441" s="25"/>
       <c r="AN441" s="1"/>
       <c r="AO441" s="1"/>
       <c r="AP441" s="1"/>
@@ -30832,7 +30839,7 @@
       <c r="AJ442" s="1"/>
       <c r="AK442" s="1"/>
       <c r="AL442" s="1"/>
-      <c r="AM442" s="1"/>
+      <c r="AM442" s="25"/>
       <c r="AN442" s="1"/>
       <c r="AO442" s="1"/>
       <c r="AP442" s="1"/>
@@ -30887,7 +30894,7 @@
       <c r="AJ443" s="1"/>
       <c r="AK443" s="1"/>
       <c r="AL443" s="1"/>
-      <c r="AM443" s="1"/>
+      <c r="AM443" s="25"/>
       <c r="AN443" s="1"/>
       <c r="AO443" s="1"/>
       <c r="AP443" s="1"/>
@@ -30942,7 +30949,7 @@
       <c r="AJ444" s="1"/>
       <c r="AK444" s="1"/>
       <c r="AL444" s="1"/>
-      <c r="AM444" s="1"/>
+      <c r="AM444" s="25"/>
       <c r="AN444" s="1"/>
       <c r="AO444" s="1"/>
       <c r="AP444" s="1"/>
@@ -30997,7 +31004,7 @@
       <c r="AJ445" s="1"/>
       <c r="AK445" s="1"/>
       <c r="AL445" s="1"/>
-      <c r="AM445" s="1"/>
+      <c r="AM445" s="25"/>
       <c r="AN445" s="1"/>
       <c r="AO445" s="1"/>
       <c r="AP445" s="1"/>
@@ -31052,7 +31059,7 @@
       <c r="AJ446" s="1"/>
       <c r="AK446" s="1"/>
       <c r="AL446" s="1"/>
-      <c r="AM446" s="1"/>
+      <c r="AM446" s="25"/>
       <c r="AN446" s="1"/>
       <c r="AO446" s="1"/>
       <c r="AP446" s="1"/>
@@ -31107,7 +31114,7 @@
       <c r="AJ447" s="1"/>
       <c r="AK447" s="1"/>
       <c r="AL447" s="1"/>
-      <c r="AM447" s="1"/>
+      <c r="AM447" s="25"/>
       <c r="AN447" s="1"/>
       <c r="AO447" s="1"/>
       <c r="AP447" s="1"/>
@@ -31162,7 +31169,7 @@
       <c r="AJ448" s="1"/>
       <c r="AK448" s="1"/>
       <c r="AL448" s="1"/>
-      <c r="AM448" s="1"/>
+      <c r="AM448" s="25"/>
       <c r="AN448" s="1"/>
       <c r="AO448" s="1"/>
       <c r="AP448" s="1"/>
@@ -31217,7 +31224,7 @@
       <c r="AJ449" s="1"/>
       <c r="AK449" s="1"/>
       <c r="AL449" s="1"/>
-      <c r="AM449" s="1"/>
+      <c r="AM449" s="25"/>
       <c r="AN449" s="1"/>
       <c r="AO449" s="1"/>
       <c r="AP449" s="1"/>
@@ -31272,7 +31279,7 @@
       <c r="AJ450" s="1"/>
       <c r="AK450" s="1"/>
       <c r="AL450" s="1"/>
-      <c r="AM450" s="1"/>
+      <c r="AM450" s="25"/>
       <c r="AN450" s="1"/>
       <c r="AO450" s="1"/>
       <c r="AP450" s="1"/>
@@ -31327,7 +31334,7 @@
       <c r="AJ451" s="1"/>
       <c r="AK451" s="1"/>
       <c r="AL451" s="1"/>
-      <c r="AM451" s="1"/>
+      <c r="AM451" s="25"/>
       <c r="AN451" s="1"/>
       <c r="AO451" s="1"/>
       <c r="AP451" s="1"/>
@@ -31382,7 +31389,7 @@
       <c r="AJ452" s="1"/>
       <c r="AK452" s="1"/>
       <c r="AL452" s="1"/>
-      <c r="AM452" s="1"/>
+      <c r="AM452" s="25"/>
       <c r="AN452" s="1"/>
       <c r="AO452" s="1"/>
       <c r="AP452" s="1"/>
@@ -31437,7 +31444,7 @@
       <c r="AJ453" s="1"/>
       <c r="AK453" s="1"/>
       <c r="AL453" s="1"/>
-      <c r="AM453" s="1"/>
+      <c r="AM453" s="25"/>
       <c r="AN453" s="1"/>
       <c r="AO453" s="1"/>
       <c r="AP453" s="1"/>
@@ -31492,7 +31499,7 @@
       <c r="AJ454" s="1"/>
       <c r="AK454" s="1"/>
       <c r="AL454" s="1"/>
-      <c r="AM454" s="1"/>
+      <c r="AM454" s="25"/>
       <c r="AN454" s="1"/>
       <c r="AO454" s="1"/>
       <c r="AP454" s="1"/>
@@ -31547,7 +31554,7 @@
       <c r="AJ455" s="1"/>
       <c r="AK455" s="1"/>
       <c r="AL455" s="1"/>
-      <c r="AM455" s="1"/>
+      <c r="AM455" s="25"/>
       <c r="AN455" s="1"/>
       <c r="AO455" s="1"/>
       <c r="AP455" s="1"/>
@@ -31602,7 +31609,7 @@
       <c r="AJ456" s="1"/>
       <c r="AK456" s="1"/>
       <c r="AL456" s="1"/>
-      <c r="AM456" s="1"/>
+      <c r="AM456" s="25"/>
       <c r="AN456" s="1"/>
       <c r="AO456" s="1"/>
       <c r="AP456" s="1"/>
@@ -31657,7 +31664,7 @@
       <c r="AJ457" s="1"/>
       <c r="AK457" s="1"/>
       <c r="AL457" s="1"/>
-      <c r="AM457" s="1"/>
+      <c r="AM457" s="25"/>
       <c r="AN457" s="1"/>
       <c r="AO457" s="1"/>
       <c r="AP457" s="1"/>
@@ -31712,7 +31719,7 @@
       <c r="AJ458" s="1"/>
       <c r="AK458" s="1"/>
       <c r="AL458" s="1"/>
-      <c r="AM458" s="1"/>
+      <c r="AM458" s="25"/>
       <c r="AN458" s="1"/>
       <c r="AO458" s="1"/>
       <c r="AP458" s="1"/>
@@ -31767,7 +31774,7 @@
       <c r="AJ459" s="1"/>
       <c r="AK459" s="1"/>
       <c r="AL459" s="1"/>
-      <c r="AM459" s="1"/>
+      <c r="AM459" s="25"/>
       <c r="AN459" s="1"/>
       <c r="AO459" s="1"/>
       <c r="AP459" s="1"/>
@@ -31822,7 +31829,7 @@
       <c r="AJ460" s="1"/>
       <c r="AK460" s="1"/>
       <c r="AL460" s="1"/>
-      <c r="AM460" s="1"/>
+      <c r="AM460" s="25"/>
       <c r="AN460" s="1"/>
       <c r="AO460" s="1"/>
       <c r="AP460" s="1"/>
@@ -31877,7 +31884,7 @@
       <c r="AJ461" s="1"/>
       <c r="AK461" s="1"/>
       <c r="AL461" s="1"/>
-      <c r="AM461" s="1"/>
+      <c r="AM461" s="25"/>
       <c r="AN461" s="1"/>
       <c r="AO461" s="1"/>
       <c r="AP461" s="1"/>
@@ -31932,7 +31939,7 @@
       <c r="AJ462" s="1"/>
       <c r="AK462" s="1"/>
       <c r="AL462" s="1"/>
-      <c r="AM462" s="1"/>
+      <c r="AM462" s="25"/>
       <c r="AN462" s="1"/>
       <c r="AO462" s="1"/>
       <c r="AP462" s="1"/>
@@ -31987,7 +31994,7 @@
       <c r="AJ463" s="1"/>
       <c r="AK463" s="1"/>
       <c r="AL463" s="1"/>
-      <c r="AM463" s="1"/>
+      <c r="AM463" s="25"/>
       <c r="AN463" s="1"/>
       <c r="AO463" s="1"/>
       <c r="AP463" s="1"/>
@@ -32042,7 +32049,7 @@
       <c r="AJ464" s="1"/>
       <c r="AK464" s="1"/>
       <c r="AL464" s="1"/>
-      <c r="AM464" s="1"/>
+      <c r="AM464" s="25"/>
       <c r="AN464" s="1"/>
       <c r="AO464" s="1"/>
       <c r="AP464" s="1"/>
@@ -32097,7 +32104,7 @@
       <c r="AJ465" s="1"/>
       <c r="AK465" s="1"/>
       <c r="AL465" s="1"/>
-      <c r="AM465" s="1"/>
+      <c r="AM465" s="25"/>
       <c r="AN465" s="1"/>
       <c r="AO465" s="1"/>
       <c r="AP465" s="1"/>
@@ -32152,7 +32159,7 @@
       <c r="AJ466" s="1"/>
       <c r="AK466" s="1"/>
       <c r="AL466" s="1"/>
-      <c r="AM466" s="1"/>
+      <c r="AM466" s="25"/>
       <c r="AN466" s="1"/>
       <c r="AO466" s="1"/>
       <c r="AP466" s="1"/>
@@ -32207,7 +32214,7 @@
       <c r="AJ467" s="1"/>
       <c r="AK467" s="1"/>
       <c r="AL467" s="1"/>
-      <c r="AM467" s="1"/>
+      <c r="AM467" s="25"/>
       <c r="AN467" s="1"/>
       <c r="AO467" s="1"/>
       <c r="AP467" s="1"/>
@@ -32262,7 +32269,7 @@
       <c r="AJ468" s="1"/>
       <c r="AK468" s="1"/>
       <c r="AL468" s="1"/>
-      <c r="AM468" s="1"/>
+      <c r="AM468" s="25"/>
       <c r="AN468" s="1"/>
       <c r="AO468" s="1"/>
       <c r="AP468" s="1"/>
@@ -32317,7 +32324,7 @@
       <c r="AJ469" s="1"/>
       <c r="AK469" s="1"/>
       <c r="AL469" s="1"/>
-      <c r="AM469" s="1"/>
+      <c r="AM469" s="25"/>
       <c r="AN469" s="1"/>
       <c r="AO469" s="1"/>
       <c r="AP469" s="1"/>
@@ -32372,7 +32379,7 @@
       <c r="AJ470" s="1"/>
       <c r="AK470" s="1"/>
       <c r="AL470" s="1"/>
-      <c r="AM470" s="1"/>
+      <c r="AM470" s="25"/>
       <c r="AN470" s="1"/>
       <c r="AO470" s="1"/>
       <c r="AP470" s="1"/>
@@ -32427,7 +32434,7 @@
       <c r="AJ471" s="1"/>
       <c r="AK471" s="1"/>
       <c r="AL471" s="1"/>
-      <c r="AM471" s="1"/>
+      <c r="AM471" s="25"/>
       <c r="AN471" s="1"/>
       <c r="AO471" s="1"/>
       <c r="AP471" s="1"/>
@@ -32482,7 +32489,7 @@
       <c r="AJ472" s="1"/>
       <c r="AK472" s="1"/>
       <c r="AL472" s="1"/>
-      <c r="AM472" s="1"/>
+      <c r="AM472" s="25"/>
       <c r="AN472" s="1"/>
       <c r="AO472" s="1"/>
       <c r="AP472" s="1"/>
@@ -32537,7 +32544,7 @@
       <c r="AJ473" s="1"/>
       <c r="AK473" s="1"/>
       <c r="AL473" s="1"/>
-      <c r="AM473" s="1"/>
+      <c r="AM473" s="25"/>
       <c r="AN473" s="1"/>
       <c r="AO473" s="1"/>
       <c r="AP473" s="1"/>
@@ -32592,7 +32599,7 @@
       <c r="AJ474" s="1"/>
       <c r="AK474" s="1"/>
       <c r="AL474" s="1"/>
-      <c r="AM474" s="1"/>
+      <c r="AM474" s="25"/>
       <c r="AN474" s="1"/>
       <c r="AO474" s="1"/>
       <c r="AP474" s="1"/>
@@ -32647,7 +32654,7 @@
       <c r="AJ475" s="1"/>
       <c r="AK475" s="1"/>
       <c r="AL475" s="1"/>
-      <c r="AM475" s="1"/>
+      <c r="AM475" s="25"/>
       <c r="AN475" s="1"/>
       <c r="AO475" s="1"/>
       <c r="AP475" s="1"/>
@@ -32702,7 +32709,7 @@
       <c r="AJ476" s="1"/>
       <c r="AK476" s="1"/>
       <c r="AL476" s="1"/>
-      <c r="AM476" s="1"/>
+      <c r="AM476" s="25"/>
       <c r="AN476" s="1"/>
       <c r="AO476" s="1"/>
       <c r="AP476" s="1"/>
@@ -32757,7 +32764,7 @@
       <c r="AJ477" s="1"/>
       <c r="AK477" s="1"/>
       <c r="AL477" s="1"/>
-      <c r="AM477" s="1"/>
+      <c r="AM477" s="25"/>
       <c r="AN477" s="1"/>
       <c r="AO477" s="1"/>
       <c r="AP477" s="1"/>
@@ -32812,7 +32819,7 @@
       <c r="AJ478" s="1"/>
       <c r="AK478" s="1"/>
       <c r="AL478" s="1"/>
-      <c r="AM478" s="1"/>
+      <c r="AM478" s="25"/>
       <c r="AN478" s="1"/>
       <c r="AO478" s="1"/>
       <c r="AP478" s="1"/>
@@ -32867,7 +32874,7 @@
       <c r="AJ479" s="1"/>
       <c r="AK479" s="1"/>
       <c r="AL479" s="1"/>
-      <c r="AM479" s="1"/>
+      <c r="AM479" s="25"/>
       <c r="AN479" s="1"/>
       <c r="AO479" s="1"/>
       <c r="AP479" s="1"/>
@@ -32922,7 +32929,7 @@
       <c r="AJ480" s="1"/>
       <c r="AK480" s="1"/>
       <c r="AL480" s="1"/>
-      <c r="AM480" s="1"/>
+      <c r="AM480" s="25"/>
       <c r="AN480" s="1"/>
       <c r="AO480" s="1"/>
       <c r="AP480" s="1"/>
@@ -32977,7 +32984,7 @@
       <c r="AJ481" s="1"/>
       <c r="AK481" s="1"/>
       <c r="AL481" s="1"/>
-      <c r="AM481" s="1"/>
+      <c r="AM481" s="25"/>
       <c r="AN481" s="1"/>
       <c r="AO481" s="1"/>
       <c r="AP481" s="1"/>
@@ -33032,7 +33039,7 @@
       <c r="AJ482" s="1"/>
       <c r="AK482" s="1"/>
       <c r="AL482" s="1"/>
-      <c r="AM482" s="1"/>
+      <c r="AM482" s="25"/>
       <c r="AN482" s="1"/>
       <c r="AO482" s="1"/>
       <c r="AP482" s="1"/>
@@ -33087,7 +33094,7 @@
       <c r="AJ483" s="1"/>
       <c r="AK483" s="1"/>
       <c r="AL483" s="1"/>
-      <c r="AM483" s="1"/>
+      <c r="AM483" s="25"/>
       <c r="AN483" s="1"/>
       <c r="AO483" s="1"/>
       <c r="AP483" s="1"/>
@@ -33142,7 +33149,7 @@
       <c r="AJ484" s="1"/>
       <c r="AK484" s="1"/>
       <c r="AL484" s="1"/>
-      <c r="AM484" s="1"/>
+      <c r="AM484" s="25"/>
       <c r="AN484" s="1"/>
       <c r="AO484" s="1"/>
       <c r="AP484" s="1"/>
@@ -33197,7 +33204,7 @@
       <c r="AJ485" s="1"/>
       <c r="AK485" s="1"/>
       <c r="AL485" s="1"/>
-      <c r="AM485" s="1"/>
+      <c r="AM485" s="25"/>
       <c r="AN485" s="1"/>
       <c r="AO485" s="1"/>
       <c r="AP485" s="1"/>
@@ -33252,7 +33259,7 @@
       <c r="AJ486" s="1"/>
       <c r="AK486" s="1"/>
       <c r="AL486" s="1"/>
-      <c r="AM486" s="1"/>
+      <c r="AM486" s="25"/>
       <c r="AN486" s="1"/>
       <c r="AO486" s="1"/>
       <c r="AP486" s="1"/>
@@ -33307,7 +33314,7 @@
       <c r="AJ487" s="1"/>
       <c r="AK487" s="1"/>
       <c r="AL487" s="1"/>
-      <c r="AM487" s="1"/>
+      <c r="AM487" s="25"/>
       <c r="AN487" s="1"/>
       <c r="AO487" s="1"/>
       <c r="AP487" s="1"/>
@@ -33362,7 +33369,7 @@
       <c r="AJ488" s="1"/>
       <c r="AK488" s="1"/>
       <c r="AL488" s="1"/>
-      <c r="AM488" s="1"/>
+      <c r="AM488" s="25"/>
       <c r="AN488" s="1"/>
       <c r="AO488" s="1"/>
       <c r="AP488" s="1"/>
@@ -33417,7 +33424,7 @@
       <c r="AJ489" s="1"/>
       <c r="AK489" s="1"/>
       <c r="AL489" s="1"/>
-      <c r="AM489" s="1"/>
+      <c r="AM489" s="25"/>
       <c r="AN489" s="1"/>
       <c r="AO489" s="1"/>
       <c r="AP489" s="1"/>
@@ -33472,7 +33479,7 @@
       <c r="AJ490" s="1"/>
       <c r="AK490" s="1"/>
       <c r="AL490" s="1"/>
-      <c r="AM490" s="1"/>
+      <c r="AM490" s="25"/>
       <c r="AN490" s="1"/>
       <c r="AO490" s="1"/>
       <c r="AP490" s="1"/>
@@ -33527,7 +33534,7 @@
       <c r="AJ491" s="1"/>
       <c r="AK491" s="1"/>
       <c r="AL491" s="1"/>
-      <c r="AM491" s="1"/>
+      <c r="AM491" s="25"/>
       <c r="AN491" s="1"/>
       <c r="AO491" s="1"/>
       <c r="AP491" s="1"/>
@@ -33582,7 +33589,7 @@
       <c r="AJ492" s="1"/>
       <c r="AK492" s="1"/>
       <c r="AL492" s="1"/>
-      <c r="AM492" s="1"/>
+      <c r="AM492" s="25"/>
       <c r="AN492" s="1"/>
       <c r="AO492" s="1"/>
       <c r="AP492" s="1"/>
@@ -33637,7 +33644,7 @@
       <c r="AJ493" s="1"/>
       <c r="AK493" s="1"/>
       <c r="AL493" s="1"/>
-      <c r="AM493" s="1"/>
+      <c r="AM493" s="25"/>
       <c r="AN493" s="1"/>
       <c r="AO493" s="1"/>
       <c r="AP493" s="1"/>
@@ -33692,7 +33699,7 @@
       <c r="AJ494" s="1"/>
       <c r="AK494" s="1"/>
       <c r="AL494" s="1"/>
-      <c r="AM494" s="1"/>
+      <c r="AM494" s="25"/>
       <c r="AN494" s="1"/>
       <c r="AO494" s="1"/>
       <c r="AP494" s="1"/>
@@ -33747,7 +33754,7 @@
       <c r="AJ495" s="1"/>
       <c r="AK495" s="1"/>
       <c r="AL495" s="1"/>
-      <c r="AM495" s="1"/>
+      <c r="AM495" s="25"/>
       <c r="AN495" s="1"/>
       <c r="AO495" s="1"/>
       <c r="AP495" s="1"/>
@@ -33802,7 +33809,7 @@
       <c r="AJ496" s="1"/>
       <c r="AK496" s="1"/>
       <c r="AL496" s="1"/>
-      <c r="AM496" s="1"/>
+      <c r="AM496" s="25"/>
       <c r="AN496" s="1"/>
       <c r="AO496" s="1"/>
       <c r="AP496" s="1"/>
@@ -33857,7 +33864,7 @@
       <c r="AJ497" s="1"/>
       <c r="AK497" s="1"/>
       <c r="AL497" s="1"/>
-      <c r="AM497" s="1"/>
+      <c r="AM497" s="25"/>
       <c r="AN497" s="1"/>
       <c r="AO497" s="1"/>
       <c r="AP497" s="1"/>
@@ -33912,7 +33919,7 @@
       <c r="AJ498" s="1"/>
       <c r="AK498" s="1"/>
       <c r="AL498" s="1"/>
-      <c r="AM498" s="1"/>
+      <c r="AM498" s="25"/>
       <c r="AN498" s="1"/>
       <c r="AO498" s="1"/>
       <c r="AP498" s="1"/>
@@ -33967,7 +33974,7 @@
       <c r="AJ499" s="1"/>
       <c r="AK499" s="1"/>
       <c r="AL499" s="1"/>
-      <c r="AM499" s="1"/>
+      <c r="AM499" s="25"/>
       <c r="AN499" s="1"/>
       <c r="AO499" s="1"/>
       <c r="AP499" s="1"/>
@@ -34022,7 +34029,7 @@
       <c r="AJ500" s="1"/>
       <c r="AK500" s="1"/>
       <c r="AL500" s="1"/>
-      <c r="AM500" s="1"/>
+      <c r="AM500" s="25"/>
       <c r="AN500" s="1"/>
       <c r="AO500" s="1"/>
       <c r="AP500" s="1"/>
